--- a/compare/output/dscale_GreenElec_downscaled_SSP434.xlsx
+++ b/compare/output/dscale_GreenElec_downscaled_SSP434.xlsx
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1473.465485</v>
+        <v>1473.465754</v>
       </c>
       <c r="F2" t="n">
-        <v>3911.171145</v>
+        <v>3911.173046</v>
       </c>
       <c r="G2" t="n">
-        <v>7738.715026</v>
+        <v>7738.723395</v>
       </c>
       <c r="H2" t="n">
-        <v>12429.554127</v>
+        <v>12429.586988</v>
       </c>
       <c r="I2" t="n">
-        <v>17302.745011</v>
+        <v>17302.906054</v>
       </c>
       <c r="J2" t="n">
         <v>2400.748955</v>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>126.444101</v>
+        <v>126.444113</v>
       </c>
       <c r="F3" t="n">
-        <v>291.425971</v>
+        <v>291.426046</v>
       </c>
       <c r="G3" t="n">
-        <v>517.990158</v>
+        <v>517.990463</v>
       </c>
       <c r="H3" t="n">
-        <v>776.644808</v>
+        <v>776.645989</v>
       </c>
       <c r="I3" t="n">
-        <v>1047.201943</v>
+        <v>1047.207825</v>
       </c>
       <c r="J3" t="n">
         <v>651.562103</v>
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>147.048334</v>
+        <v>147.048245</v>
       </c>
       <c r="F4" t="n">
-        <v>315.062757</v>
+        <v>315.062296</v>
       </c>
       <c r="G4" t="n">
-        <v>505.359487</v>
+        <v>505.358061</v>
       </c>
       <c r="H4" t="n">
-        <v>702.846998</v>
+        <v>702.842789</v>
       </c>
       <c r="I4" t="n">
-        <v>902.463521</v>
+        <v>902.446243</v>
       </c>
       <c r="J4" t="n">
         <v>3343.297015</v>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>78.152179</v>
+        <v>78.152151</v>
       </c>
       <c r="F5" t="n">
-        <v>244.488495</v>
+        <v>244.488079</v>
       </c>
       <c r="G5" t="n">
-        <v>607.347125</v>
+        <v>607.342993</v>
       </c>
       <c r="H5" t="n">
-        <v>1165.166713</v>
+        <v>1165.139054</v>
       </c>
       <c r="I5" t="n">
-        <v>1841.93262</v>
+        <v>1841.745778</v>
       </c>
       <c r="J5" t="n">
         <v>33153.574944</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>37125.795121</v>
+        <v>37125.800951</v>
       </c>
       <c r="F6" t="n">
-        <v>98137.653345</v>
+        <v>98137.692985</v>
       </c>
       <c r="G6" t="n">
-        <v>177921.858825</v>
+        <v>177922.020578</v>
       </c>
       <c r="H6" t="n">
-        <v>267311.932934</v>
+        <v>267312.540371</v>
       </c>
       <c r="I6" t="n">
-        <v>362716.567174</v>
+        <v>362719.5086</v>
       </c>
       <c r="J6" t="n">
         <v>106673.096499</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>29573.463276</v>
+        <v>29573.467047</v>
       </c>
       <c r="F7" t="n">
-        <v>80682.30994200001</v>
+        <v>80682.33416499999</v>
       </c>
       <c r="G7" t="n">
-        <v>169135.030282</v>
+        <v>169135.12329</v>
       </c>
       <c r="H7" t="n">
-        <v>291288.689122</v>
+        <v>291289.008488</v>
       </c>
       <c r="I7" t="n">
-        <v>439361.385708</v>
+        <v>439362.752458</v>
       </c>
       <c r="J7" t="n">
         <v>507983.544619</v>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3381.854424</v>
+        <v>3381.854799</v>
       </c>
       <c r="F8" t="n">
-        <v>9125.601191</v>
+        <v>9125.603531999999</v>
       </c>
       <c r="G8" t="n">
-        <v>18687.684468</v>
+        <v>18687.693362</v>
       </c>
       <c r="H8" t="n">
-        <v>31415.895722</v>
+        <v>31415.927413</v>
       </c>
       <c r="I8" t="n">
-        <v>46223.069879</v>
+        <v>46223.217622</v>
       </c>
       <c r="J8" t="n">
         <v>48827.502294</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2419.179969</v>
+        <v>2419.172464</v>
       </c>
       <c r="F9" t="n">
-        <v>5004.271107</v>
+        <v>5004.231034</v>
       </c>
       <c r="G9" t="n">
-        <v>7577.622118</v>
+        <v>7577.500713</v>
       </c>
       <c r="H9" t="n">
-        <v>9797.771898999999</v>
+        <v>9797.434401</v>
       </c>
       <c r="I9" t="n">
-        <v>11673.594067</v>
+        <v>11672.320122</v>
       </c>
       <c r="J9" t="n">
         <v>161060.597402</v>
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1072.815753</v>
+        <v>1072.815607</v>
       </c>
       <c r="F10" t="n">
-        <v>2548.521972</v>
+        <v>2548.521051</v>
       </c>
       <c r="G10" t="n">
-        <v>4378.617524</v>
+        <v>4378.614645</v>
       </c>
       <c r="H10" t="n">
-        <v>6474.330937</v>
+        <v>6474.322804</v>
       </c>
       <c r="I10" t="n">
-        <v>8701.587511</v>
+        <v>8701.557766</v>
       </c>
       <c r="J10" t="n">
         <v>15447.103693</v>
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>29960.687954</v>
+        <v>29960.684328</v>
       </c>
       <c r="F11" t="n">
-        <v>76382.189315</v>
+        <v>76382.15574</v>
       </c>
       <c r="G11" t="n">
-        <v>145790.559638</v>
+        <v>145790.385624</v>
       </c>
       <c r="H11" t="n">
-        <v>232503.467298</v>
+        <v>232502.720963</v>
       </c>
       <c r="I11" t="n">
-        <v>326629.97766</v>
+        <v>326626.168105</v>
       </c>
       <c r="J11" t="n">
         <v>969650.01117</v>
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1585.370954</v>
+        <v>1585.371227</v>
       </c>
       <c r="F12" t="n">
-        <v>4258.209551</v>
+        <v>4258.211467</v>
       </c>
       <c r="G12" t="n">
-        <v>8709.517900000001</v>
+        <v>8709.526422999999</v>
       </c>
       <c r="H12" t="n">
-        <v>14748.202514</v>
+        <v>14748.23704</v>
       </c>
       <c r="I12" t="n">
-        <v>21686.716086</v>
+        <v>21686.891841</v>
       </c>
       <c r="J12" t="n">
         <v>7364.116009</v>
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>12298.299449</v>
+        <v>12298.300313</v>
       </c>
       <c r="F13" t="n">
-        <v>31636.406911</v>
+        <v>31636.41226</v>
       </c>
       <c r="G13" t="n">
-        <v>59847.77175</v>
+        <v>59847.794754</v>
       </c>
       <c r="H13" t="n">
-        <v>95946.978227</v>
+        <v>95947.075</v>
       </c>
       <c r="I13" t="n">
-        <v>138940.350119</v>
+        <v>138940.868888</v>
       </c>
       <c r="J13" t="n">
         <v>130824.296596</v>
@@ -1438,19 +1438,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>800.061194</v>
+        <v>800.02118</v>
       </c>
       <c r="F14" t="n">
-        <v>2107.930606</v>
+        <v>2107.660855</v>
       </c>
       <c r="G14" t="n">
-        <v>5071.901581</v>
+        <v>5070.550523</v>
       </c>
       <c r="H14" t="n">
-        <v>8844.876177</v>
+        <v>8839.860438</v>
       </c>
       <c r="I14" t="n">
-        <v>14038.461536</v>
+        <v>14016.911943</v>
       </c>
       <c r="J14" t="n">
         <v>432066.740405</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>56958.180658</v>
+        <v>56958.262333</v>
       </c>
       <c r="F15" t="n">
-        <v>165729.189603</v>
+        <v>165729.677935</v>
       </c>
       <c r="G15" t="n">
-        <v>418279.315591</v>
+        <v>418281.42093</v>
       </c>
       <c r="H15" t="n">
-        <v>743630.951363</v>
+        <v>743638.018133</v>
       </c>
       <c r="I15" t="n">
-        <v>1182366.190243</v>
+        <v>1182395.00175</v>
       </c>
       <c r="J15" t="n">
         <v>1096632.104521</v>
@@ -1590,19 +1590,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>28.932501</v>
+        <v>28.868256</v>
       </c>
       <c r="F16" t="n">
-        <v>67.44057599999999</v>
+        <v>67.107626</v>
       </c>
       <c r="G16" t="n">
-        <v>139.239209</v>
+        <v>138.032658</v>
       </c>
       <c r="H16" t="n">
-        <v>216.937657</v>
+        <v>213.465744</v>
       </c>
       <c r="I16" t="n">
-        <v>327.344957</v>
+        <v>314.907024</v>
       </c>
       <c r="J16" t="n">
         <v>211228.177552</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>15888.166105</v>
+        <v>15888.199268</v>
       </c>
       <c r="F17" t="n">
-        <v>41622.814376</v>
+        <v>41623.019289</v>
       </c>
       <c r="G17" t="n">
-        <v>96256.42088200001</v>
+        <v>96257.339609</v>
       </c>
       <c r="H17" t="n">
-        <v>159268.183069</v>
+        <v>159271.298067</v>
       </c>
       <c r="I17" t="n">
-        <v>237832.678731</v>
+        <v>237845.080904</v>
       </c>
       <c r="J17" t="n">
         <v>87487.71411</v>
@@ -1742,19 +1742,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1992.599476</v>
+        <v>1992.588899</v>
       </c>
       <c r="F18" t="n">
-        <v>5660.090099</v>
+        <v>5659.999554</v>
       </c>
       <c r="G18" t="n">
-        <v>13524.075136</v>
+        <v>13523.60868</v>
       </c>
       <c r="H18" t="n">
-        <v>23023.097035</v>
+        <v>23021.402918</v>
       </c>
       <c r="I18" t="n">
-        <v>35927.178833</v>
+        <v>35919.95268</v>
       </c>
       <c r="J18" t="n">
         <v>194952.217712</v>
@@ -1818,58 +1818,58 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>18776.99441</v>
+        <v>18776.992584</v>
       </c>
       <c r="F19" t="n">
-        <v>27192.634438</v>
+        <v>27192.628389</v>
       </c>
       <c r="G19" t="n">
-        <v>40721.373628</v>
+        <v>40721.358695</v>
       </c>
       <c r="H19" t="n">
-        <v>59702.38403</v>
+        <v>59702.351827</v>
       </c>
       <c r="I19" t="n">
-        <v>76146.004222</v>
+        <v>76145.94663999999</v>
       </c>
       <c r="J19" t="n">
-        <v>94235.08282900001</v>
+        <v>94234.985527</v>
       </c>
       <c r="K19" t="n">
-        <v>118096.441611</v>
+        <v>118096.277943</v>
       </c>
       <c r="L19" t="n">
-        <v>149485.001137</v>
+        <v>149484.726025</v>
       </c>
       <c r="M19" t="n">
-        <v>192675.696768</v>
+        <v>192675.227568</v>
       </c>
       <c r="N19" t="n">
-        <v>249872.547899</v>
+        <v>249871.744188</v>
       </c>
       <c r="O19" t="n">
-        <v>323750.508925</v>
+        <v>323749.137269</v>
       </c>
       <c r="P19" t="n">
-        <v>411525.999097</v>
+        <v>411523.708223</v>
       </c>
       <c r="Q19" t="n">
-        <v>513170.230802</v>
+        <v>513166.477622</v>
       </c>
       <c r="R19" t="n">
-        <v>628991.361672</v>
+        <v>628985.296931</v>
       </c>
       <c r="S19" t="n">
-        <v>759506.2130540001</v>
+        <v>759496.47557</v>
       </c>
       <c r="T19" t="n">
-        <v>909271.415485</v>
+        <v>909255.6701700001</v>
       </c>
       <c r="U19" t="n">
-        <v>1061255.218901</v>
+        <v>1061229.811341</v>
       </c>
       <c r="V19" t="n">
-        <v>1174229.319412</v>
+        <v>1174188.978025</v>
       </c>
     </row>
     <row r="20">
@@ -1894,58 +1894,58 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10.683124</v>
+        <v>10.682137</v>
       </c>
       <c r="F20" t="n">
-        <v>14.964852</v>
+        <v>14.961432</v>
       </c>
       <c r="G20" t="n">
-        <v>22.581291</v>
+        <v>22.571608</v>
       </c>
       <c r="H20" t="n">
-        <v>32.519127</v>
+        <v>32.49656</v>
       </c>
       <c r="I20" t="n">
-        <v>39.80284</v>
+        <v>39.761904</v>
       </c>
       <c r="J20" t="n">
-        <v>46.392581</v>
+        <v>46.325809</v>
       </c>
       <c r="K20" t="n">
-        <v>53.607482</v>
+        <v>53.504242</v>
       </c>
       <c r="L20" t="n">
-        <v>61.526708</v>
+        <v>61.373523</v>
       </c>
       <c r="M20" t="n">
-        <v>71.20822099999999</v>
+        <v>70.984229</v>
       </c>
       <c r="N20" t="n">
-        <v>82.809033</v>
+        <v>82.484292</v>
       </c>
       <c r="O20" t="n">
-        <v>96.57483999999999</v>
+        <v>96.105498</v>
       </c>
       <c r="P20" t="n">
-        <v>111.115395</v>
+        <v>110.448099</v>
       </c>
       <c r="Q20" t="n">
-        <v>126.019945</v>
+        <v>125.086311</v>
       </c>
       <c r="R20" t="n">
-        <v>141.276874</v>
+        <v>139.986409</v>
       </c>
       <c r="S20" t="n">
-        <v>157.133273</v>
+        <v>155.358149</v>
       </c>
       <c r="T20" t="n">
-        <v>175.351576</v>
+        <v>172.886253</v>
       </c>
       <c r="U20" t="n">
-        <v>193.593166</v>
+        <v>190.173899</v>
       </c>
       <c r="V20" t="n">
-        <v>207.659283</v>
+        <v>202.991014</v>
       </c>
     </row>
     <row r="21">
@@ -1970,58 +1970,58 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>345.807721</v>
+        <v>345.807713</v>
       </c>
       <c r="F21" t="n">
-        <v>398.859198</v>
+        <v>398.859183</v>
       </c>
       <c r="G21" t="n">
-        <v>498.959587</v>
+        <v>498.959564</v>
       </c>
       <c r="H21" t="n">
-        <v>647.259721</v>
+        <v>647.259682</v>
       </c>
       <c r="I21" t="n">
-        <v>761.0790950000001</v>
+        <v>761.079028</v>
       </c>
       <c r="J21" t="n">
-        <v>889.23617</v>
+        <v>889.236048</v>
       </c>
       <c r="K21" t="n">
-        <v>1059.458019</v>
+        <v>1059.457796</v>
       </c>
       <c r="L21" t="n">
-        <v>1279.032498</v>
+        <v>1279.032101</v>
       </c>
       <c r="M21" t="n">
-        <v>1578.148145</v>
+        <v>1578.147433</v>
       </c>
       <c r="N21" t="n">
-        <v>1976.224081</v>
+        <v>1976.222792</v>
       </c>
       <c r="O21" t="n">
-        <v>2496.973009</v>
+        <v>2496.970665</v>
       </c>
       <c r="P21" t="n">
-        <v>3128.589819</v>
+        <v>3128.585603</v>
       </c>
       <c r="Q21" t="n">
-        <v>3877.122716</v>
+        <v>3877.115259</v>
       </c>
       <c r="R21" t="n">
-        <v>4758.923465</v>
+        <v>4758.910423</v>
       </c>
       <c r="S21" t="n">
-        <v>5779.240076</v>
+        <v>5779.217452</v>
       </c>
       <c r="T21" t="n">
-        <v>6992.376414</v>
+        <v>6992.336992</v>
       </c>
       <c r="U21" t="n">
-        <v>8266.694443</v>
+        <v>8266.626270000001</v>
       </c>
       <c r="V21" t="n">
-        <v>9304.159755999999</v>
+        <v>9304.043835</v>
       </c>
     </row>
     <row r="22">
@@ -2046,58 +2046,58 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>61271.452829</v>
+        <v>61271.454519</v>
       </c>
       <c r="F22" t="n">
-        <v>89799.49354900001</v>
+        <v>89799.499285</v>
       </c>
       <c r="G22" t="n">
-        <v>134727.998059</v>
+        <v>134728.012737</v>
       </c>
       <c r="H22" t="n">
-        <v>196261.76693</v>
+        <v>196261.798889</v>
       </c>
       <c r="I22" t="n">
-        <v>247460.996904</v>
+        <v>247461.052909</v>
       </c>
       <c r="J22" t="n">
-        <v>302815.801079</v>
+        <v>302815.892196</v>
       </c>
       <c r="K22" t="n">
-        <v>375135.641272</v>
+        <v>375135.787031</v>
       </c>
       <c r="L22" t="n">
-        <v>468031.887029</v>
+        <v>468032.118116</v>
       </c>
       <c r="M22" t="n">
-        <v>593015.477715</v>
+        <v>593015.84753</v>
       </c>
       <c r="N22" t="n">
-        <v>756301.6515790001</v>
+        <v>756302.246495</v>
       </c>
       <c r="O22" t="n">
-        <v>965951.773848</v>
+        <v>965952.730887</v>
       </c>
       <c r="P22" t="n">
-        <v>1215450.271956</v>
+        <v>1215451.78636</v>
       </c>
       <c r="Q22" t="n">
-        <v>1505462.590621</v>
+        <v>1505464.95061</v>
       </c>
       <c r="R22" t="n">
-        <v>1840823.36012</v>
+        <v>1840827.003476</v>
       </c>
       <c r="S22" t="n">
-        <v>2223960.839647</v>
+        <v>2223966.452479</v>
       </c>
       <c r="T22" t="n">
-        <v>2674650.161563</v>
+        <v>2674658.90418</v>
       </c>
       <c r="U22" t="n">
-        <v>3142416.476763</v>
+        <v>3142430.108491</v>
       </c>
       <c r="V22" t="n">
-        <v>3514565.728091</v>
+        <v>3514586.719675</v>
       </c>
     </row>
     <row r="23">
@@ -2122,58 +2122,58 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2648.601103</v>
+        <v>2648.601135</v>
       </c>
       <c r="F23" t="n">
-        <v>4140.10719</v>
+        <v>4140.107297</v>
       </c>
       <c r="G23" t="n">
-        <v>6779.615596</v>
+        <v>6779.615869</v>
       </c>
       <c r="H23" t="n">
-        <v>10970.284052</v>
+        <v>10970.284632</v>
       </c>
       <c r="I23" t="n">
-        <v>15463.196746</v>
+        <v>15463.197683</v>
       </c>
       <c r="J23" t="n">
-        <v>21051.935654</v>
+        <v>21051.936945</v>
       </c>
       <c r="K23" t="n">
-        <v>28777.636648</v>
+        <v>28777.638159</v>
       </c>
       <c r="L23" t="n">
-        <v>39508.445825</v>
+        <v>39508.447004</v>
       </c>
       <c r="M23" t="n">
-        <v>54925.182405</v>
+        <v>54925.181767</v>
       </c>
       <c r="N23" t="n">
-        <v>76460.62430900001</v>
+        <v>76460.618332</v>
       </c>
       <c r="O23" t="n">
-        <v>106031.066686</v>
+        <v>106031.04757</v>
       </c>
       <c r="P23" t="n">
-        <v>143952.714719</v>
+        <v>143952.666506</v>
       </c>
       <c r="Q23" t="n">
-        <v>191074.723954</v>
+        <v>191074.616751</v>
       </c>
       <c r="R23" t="n">
-        <v>248450.797631</v>
+        <v>248450.575976</v>
       </c>
       <c r="S23" t="n">
-        <v>316943.835398</v>
+        <v>316943.399797</v>
       </c>
       <c r="T23" t="n">
-        <v>400193.437081</v>
+        <v>400192.600187</v>
       </c>
       <c r="U23" t="n">
-        <v>490974.450601</v>
+        <v>490972.882912</v>
       </c>
       <c r="V23" t="n">
-        <v>570766.696708</v>
+        <v>570763.848754</v>
       </c>
     </row>
     <row r="24">
@@ -2198,58 +2198,58 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5392.290035</v>
+        <v>5392.28988</v>
       </c>
       <c r="F24" t="n">
-        <v>7355.108608</v>
+        <v>7355.108113</v>
       </c>
       <c r="G24" t="n">
-        <v>10726.020926</v>
+        <v>10726.019636</v>
       </c>
       <c r="H24" t="n">
-        <v>15305.695693</v>
+        <v>15305.692778</v>
       </c>
       <c r="I24" t="n">
-        <v>18979.25255</v>
+        <v>18979.247116</v>
       </c>
       <c r="J24" t="n">
-        <v>22745.493182</v>
+        <v>22745.483751</v>
       </c>
       <c r="K24" t="n">
-        <v>27415.055706</v>
+        <v>27415.039764</v>
       </c>
       <c r="L24" t="n">
-        <v>33055.603576</v>
+        <v>33055.577542</v>
       </c>
       <c r="M24" t="n">
-        <v>40229.054782</v>
+        <v>40229.013061</v>
       </c>
       <c r="N24" t="n">
-        <v>49123.164492</v>
+        <v>49123.098427</v>
       </c>
       <c r="O24" t="n">
-        <v>60092.537523</v>
+        <v>60092.433179</v>
       </c>
       <c r="P24" t="n">
-        <v>72554.848831</v>
+        <v>72554.68616899999</v>
       </c>
       <c r="Q24" t="n">
-        <v>86135.46084</v>
+        <v>86135.211329</v>
       </c>
       <c r="R24" t="n">
-        <v>100992.018199</v>
+        <v>100991.638982</v>
       </c>
       <c r="S24" t="n">
-        <v>117130.193244</v>
+        <v>117129.616951</v>
       </c>
       <c r="T24" t="n">
-        <v>135342.198035</v>
+        <v>135341.309653</v>
       </c>
       <c r="U24" t="n">
-        <v>152884.66953</v>
+        <v>152883.301167</v>
       </c>
       <c r="V24" t="n">
-        <v>164394.215532</v>
+        <v>164392.134514</v>
       </c>
     </row>
     <row r="25">
@@ -2274,58 +2274,58 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1291.161788</v>
+        <v>1291.161751</v>
       </c>
       <c r="F25" t="n">
-        <v>1578.732706</v>
+        <v>1578.732619</v>
       </c>
       <c r="G25" t="n">
-        <v>2092.306349</v>
+        <v>2092.306172</v>
       </c>
       <c r="H25" t="n">
-        <v>2824.116364</v>
+        <v>2824.116008</v>
       </c>
       <c r="I25" t="n">
-        <v>3396.744616</v>
+        <v>3396.743974</v>
       </c>
       <c r="J25" t="n">
-        <v>3984.534381</v>
+        <v>3984.53328</v>
       </c>
       <c r="K25" t="n">
-        <v>4731.410904</v>
+        <v>4731.409052</v>
       </c>
       <c r="L25" t="n">
-        <v>5632.97204</v>
+        <v>5632.969019</v>
       </c>
       <c r="M25" t="n">
-        <v>6817.056157</v>
+        <v>6817.051247</v>
       </c>
       <c r="N25" t="n">
-        <v>8389.818255</v>
+        <v>8389.810127000001</v>
       </c>
       <c r="O25" t="n">
-        <v>10457.746108</v>
+        <v>10457.732307</v>
       </c>
       <c r="P25" t="n">
-        <v>12981.048086</v>
+        <v>12981.024665</v>
       </c>
       <c r="Q25" t="n">
-        <v>15978.319099</v>
+        <v>15978.279644</v>
       </c>
       <c r="R25" t="n">
-        <v>19486.451603</v>
+        <v>19486.38556</v>
       </c>
       <c r="S25" t="n">
-        <v>23511.857044</v>
+        <v>23511.747322</v>
       </c>
       <c r="T25" t="n">
-        <v>28234.813675</v>
+        <v>28234.630208</v>
       </c>
       <c r="U25" t="n">
-        <v>33076.585576</v>
+        <v>33076.281469</v>
       </c>
       <c r="V25" t="n">
-        <v>36791.808767</v>
+        <v>36791.315091</v>
       </c>
     </row>
     <row r="26">
@@ -2350,58 +2350,58 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7807.438579</v>
+        <v>7807.438341</v>
       </c>
       <c r="F26" t="n">
-        <v>10884.707997</v>
+        <v>10884.70729</v>
       </c>
       <c r="G26" t="n">
-        <v>15427.685993</v>
+        <v>15427.684536</v>
       </c>
       <c r="H26" t="n">
-        <v>21757.115795</v>
+        <v>21757.113059</v>
       </c>
       <c r="I26" t="n">
-        <v>27047.688591</v>
+        <v>27047.684129</v>
       </c>
       <c r="J26" t="n">
-        <v>33007.210502</v>
+        <v>33007.20331</v>
       </c>
       <c r="K26" t="n">
-        <v>41092.593186</v>
+        <v>41092.581202</v>
       </c>
       <c r="L26" t="n">
-        <v>52114.842845</v>
+        <v>52114.822195</v>
       </c>
       <c r="M26" t="n">
-        <v>67542.727662</v>
+        <v>67542.69107299999</v>
       </c>
       <c r="N26" t="n">
-        <v>88141.263135</v>
+        <v>88141.19824500001</v>
       </c>
       <c r="O26" t="n">
-        <v>114799.827595</v>
+        <v>114799.713967</v>
       </c>
       <c r="P26" t="n">
-        <v>146615.662576</v>
+        <v>146615.469506</v>
       </c>
       <c r="Q26" t="n">
-        <v>183365.904245</v>
+        <v>183365.584854</v>
       </c>
       <c r="R26" t="n">
-        <v>225371.778947</v>
+        <v>225371.25974</v>
       </c>
       <c r="S26" t="n">
-        <v>272976.874438</v>
+        <v>272976.037771</v>
       </c>
       <c r="T26" t="n">
-        <v>328634.157904</v>
+        <v>328632.796125</v>
       </c>
       <c r="U26" t="n">
-        <v>385943.466506</v>
+        <v>385941.254695</v>
       </c>
       <c r="V26" t="n">
-        <v>430712.390894</v>
+        <v>430708.847128</v>
       </c>
     </row>
     <row r="27">
@@ -2426,58 +2426,58 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>46599.17374</v>
+        <v>46599.174733</v>
       </c>
       <c r="F27" t="n">
-        <v>66675.28559699999</v>
+        <v>66675.288933</v>
       </c>
       <c r="G27" t="n">
-        <v>96161.68098</v>
+        <v>96161.689386</v>
       </c>
       <c r="H27" t="n">
-        <v>137657.117014</v>
+        <v>137657.135279</v>
       </c>
       <c r="I27" t="n">
-        <v>174849.639047</v>
+        <v>174849.671488</v>
       </c>
       <c r="J27" t="n">
-        <v>218527.567401</v>
+        <v>218527.621282</v>
       </c>
       <c r="K27" t="n">
-        <v>277724.35856</v>
+        <v>277724.446546</v>
       </c>
       <c r="L27" t="n">
-        <v>357014.70857</v>
+        <v>357014.851306</v>
       </c>
       <c r="M27" t="n">
-        <v>469358.143749</v>
+        <v>469358.378197</v>
       </c>
       <c r="N27" t="n">
-        <v>622836.05027</v>
+        <v>622836.437595</v>
       </c>
       <c r="O27" t="n">
-        <v>826613.97507</v>
+        <v>826614.614257</v>
       </c>
       <c r="P27" t="n">
-        <v>1076237.573562</v>
+        <v>1076238.606746</v>
       </c>
       <c r="Q27" t="n">
-        <v>1372579.328433</v>
+        <v>1372580.965704</v>
       </c>
       <c r="R27" t="n">
-        <v>1718608.627226</v>
+        <v>1718611.185029</v>
       </c>
       <c r="S27" t="n">
-        <v>2114725.653196</v>
+        <v>2114729.62101</v>
       </c>
       <c r="T27" t="n">
-        <v>2581154.069382</v>
+        <v>2581160.273912</v>
       </c>
       <c r="U27" t="n">
-        <v>3068235.08206</v>
+        <v>3068244.76863</v>
       </c>
       <c r="V27" t="n">
-        <v>3461589.126034</v>
+        <v>3461604.011152</v>
       </c>
     </row>
     <row r="28">
@@ -2502,58 +2502,58 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>18204.300972</v>
+        <v>18204.301507</v>
       </c>
       <c r="F28" t="n">
-        <v>23372.124662</v>
+        <v>23372.126256</v>
       </c>
       <c r="G28" t="n">
-        <v>36092.009236</v>
+        <v>36092.01344</v>
       </c>
       <c r="H28" t="n">
-        <v>57467.448667</v>
+        <v>57467.458678</v>
       </c>
       <c r="I28" t="n">
-        <v>81422.573982</v>
+        <v>81422.593721</v>
       </c>
       <c r="J28" t="n">
-        <v>110323.738814</v>
+        <v>110323.774444</v>
       </c>
       <c r="K28" t="n">
-        <v>147430.832605</v>
+        <v>147430.894257</v>
       </c>
       <c r="L28" t="n">
-        <v>194015.852765</v>
+        <v>194015.956161</v>
       </c>
       <c r="M28" t="n">
-        <v>257095.481696</v>
+        <v>257095.655195</v>
       </c>
       <c r="N28" t="n">
-        <v>342881.928949</v>
+        <v>342882.221507</v>
       </c>
       <c r="O28" t="n">
-        <v>462296.236396</v>
+        <v>462296.734399</v>
       </c>
       <c r="P28" t="n">
-        <v>620247.705958</v>
+        <v>620248.548125</v>
       </c>
       <c r="Q28" t="n">
-        <v>824867.253546</v>
+        <v>824868.666115</v>
       </c>
       <c r="R28" t="n">
-        <v>1085622.252463</v>
+        <v>1085624.605676</v>
       </c>
       <c r="S28" t="n">
-        <v>1411934.16723</v>
+        <v>1411938.080099</v>
       </c>
       <c r="T28" t="n">
-        <v>1826483.039203</v>
+        <v>1826489.612639</v>
       </c>
       <c r="U28" t="n">
-        <v>2302750.591424</v>
+        <v>2302761.620095</v>
       </c>
       <c r="V28" t="n">
-        <v>2754351.032067</v>
+        <v>2754369.247355</v>
       </c>
     </row>
     <row r="29">
@@ -2581,55 +2581,55 @@
         <v>22.251794</v>
       </c>
       <c r="F29" t="n">
-        <v>35.164275</v>
+        <v>35.164274</v>
       </c>
       <c r="G29" t="n">
-        <v>51.272494</v>
+        <v>51.272493</v>
       </c>
       <c r="H29" t="n">
-        <v>72.438912</v>
+        <v>72.438909</v>
       </c>
       <c r="I29" t="n">
-        <v>98.986869</v>
+        <v>98.986863</v>
       </c>
       <c r="J29" t="n">
-        <v>133.62379</v>
+        <v>133.623779</v>
       </c>
       <c r="K29" t="n">
-        <v>182.714309</v>
+        <v>182.714285</v>
       </c>
       <c r="L29" t="n">
-        <v>247.495942</v>
+        <v>247.495894</v>
       </c>
       <c r="M29" t="n">
-        <v>330.147336</v>
+        <v>330.147241</v>
       </c>
       <c r="N29" t="n">
-        <v>440.419049</v>
+        <v>440.418859</v>
       </c>
       <c r="O29" t="n">
-        <v>585.008992</v>
+        <v>585.008617</v>
       </c>
       <c r="P29" t="n">
-        <v>765.681945</v>
+        <v>765.681211</v>
       </c>
       <c r="Q29" t="n">
-        <v>986.108164</v>
+        <v>986.1067410000001</v>
       </c>
       <c r="R29" t="n">
-        <v>1248.746671</v>
+        <v>1248.743928</v>
       </c>
       <c r="S29" t="n">
-        <v>1550.1402</v>
+        <v>1550.134901</v>
       </c>
       <c r="T29" t="n">
-        <v>1886.411551</v>
+        <v>1886.401204</v>
       </c>
       <c r="U29" t="n">
-        <v>2263.465183</v>
+        <v>2263.444279</v>
       </c>
       <c r="V29" t="n">
-        <v>2640.011572</v>
+        <v>2639.967459</v>
       </c>
     </row>
     <row r="30">
@@ -2660,52 +2660,52 @@
         <v>526.541511</v>
       </c>
       <c r="G30" t="n">
-        <v>622.376988</v>
+        <v>622.376989</v>
       </c>
       <c r="H30" t="n">
-        <v>781.530401</v>
+        <v>781.530403</v>
       </c>
       <c r="I30" t="n">
-        <v>1022.87471</v>
+        <v>1022.874714</v>
       </c>
       <c r="J30" t="n">
-        <v>1389.033402</v>
+        <v>1389.033408</v>
       </c>
       <c r="K30" t="n">
-        <v>1955.134865</v>
+        <v>1955.134878</v>
       </c>
       <c r="L30" t="n">
-        <v>2749.825228</v>
+        <v>2749.825253</v>
       </c>
       <c r="M30" t="n">
-        <v>3819.899987</v>
+        <v>3819.90004</v>
       </c>
       <c r="N30" t="n">
-        <v>5306.589889</v>
+        <v>5306.589993</v>
       </c>
       <c r="O30" t="n">
-        <v>7338.261319</v>
+        <v>7338.261514</v>
       </c>
       <c r="P30" t="n">
-        <v>10000.587701</v>
+        <v>10000.588057</v>
       </c>
       <c r="Q30" t="n">
-        <v>13431.455228</v>
+        <v>13431.455876</v>
       </c>
       <c r="R30" t="n">
-        <v>17758.544109</v>
+        <v>17758.5453</v>
       </c>
       <c r="S30" t="n">
-        <v>23043.024408</v>
+        <v>23043.026619</v>
       </c>
       <c r="T30" t="n">
-        <v>29288.870759</v>
+        <v>29288.874922</v>
       </c>
       <c r="U30" t="n">
-        <v>36684.867669</v>
+        <v>36684.875717</v>
       </c>
       <c r="V30" t="n">
-        <v>44588.864934</v>
+        <v>44588.880951</v>
       </c>
     </row>
     <row r="31">
@@ -2730,58 +2730,58 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>768.595853</v>
+        <v>768.595854</v>
       </c>
       <c r="F31" t="n">
-        <v>1169.897946</v>
+        <v>1169.897947</v>
       </c>
       <c r="G31" t="n">
-        <v>1574.380694</v>
+        <v>1574.380697</v>
       </c>
       <c r="H31" t="n">
-        <v>2096.976126</v>
+        <v>2096.976132</v>
       </c>
       <c r="I31" t="n">
-        <v>2737.156746</v>
+        <v>2737.156756</v>
       </c>
       <c r="J31" t="n">
-        <v>3564.673848</v>
+        <v>3564.673867</v>
       </c>
       <c r="K31" t="n">
-        <v>4719.936147</v>
+        <v>4719.936182</v>
       </c>
       <c r="L31" t="n">
-        <v>6205.555825</v>
+        <v>6205.555894</v>
       </c>
       <c r="M31" t="n">
-        <v>8088.649998</v>
+        <v>8088.650132</v>
       </c>
       <c r="N31" t="n">
-        <v>10649.83775</v>
+        <v>10649.838005</v>
       </c>
       <c r="O31" t="n">
-        <v>14072.454888</v>
+        <v>14072.455359</v>
       </c>
       <c r="P31" t="n">
-        <v>18404.87596</v>
+        <v>18404.876811</v>
       </c>
       <c r="Q31" t="n">
-        <v>23750.421187</v>
+        <v>23750.422728</v>
       </c>
       <c r="R31" t="n">
-        <v>30141.676265</v>
+        <v>30141.679086</v>
       </c>
       <c r="S31" t="n">
-        <v>37516.07487</v>
+        <v>37516.080089</v>
       </c>
       <c r="T31" t="n">
-        <v>45758.296482</v>
+        <v>45758.30631</v>
       </c>
       <c r="U31" t="n">
-        <v>55054.531795</v>
+        <v>55054.550911</v>
       </c>
       <c r="V31" t="n">
-        <v>64411.068757</v>
+        <v>64411.107448</v>
       </c>
     </row>
     <row r="32">
@@ -2806,58 +2806,58 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5403.47713</v>
+        <v>5403.477134</v>
       </c>
       <c r="F32" t="n">
-        <v>7552.582896</v>
+        <v>7552.582906</v>
       </c>
       <c r="G32" t="n">
-        <v>9715.544707999999</v>
+        <v>9715.544727</v>
       </c>
       <c r="H32" t="n">
-        <v>12622.379215</v>
+        <v>12622.379247</v>
       </c>
       <c r="I32" t="n">
-        <v>16434.899916</v>
+        <v>16434.899971</v>
       </c>
       <c r="J32" t="n">
-        <v>21661.673487</v>
+        <v>21661.673588</v>
       </c>
       <c r="K32" t="n">
-        <v>29301.622646</v>
+        <v>29301.622843</v>
       </c>
       <c r="L32" t="n">
-        <v>39473.739906</v>
+        <v>39473.740299</v>
       </c>
       <c r="M32" t="n">
-        <v>52666.166151</v>
+        <v>52666.166938</v>
       </c>
       <c r="N32" t="n">
-        <v>70580.96872200001</v>
+        <v>70580.97022800001</v>
       </c>
       <c r="O32" t="n">
-        <v>94519.64464899999</v>
+        <v>94519.647423</v>
       </c>
       <c r="P32" t="n">
-        <v>124916.804119</v>
+        <v>124916.809104</v>
       </c>
       <c r="Q32" t="n">
-        <v>162769.059316</v>
+        <v>162769.068284</v>
       </c>
       <c r="R32" t="n">
-        <v>208776.010401</v>
+        <v>208776.026749</v>
       </c>
       <c r="S32" t="n">
-        <v>262841.60687</v>
+        <v>262841.637067</v>
       </c>
       <c r="T32" t="n">
-        <v>324636.220721</v>
+        <v>324636.277592</v>
       </c>
       <c r="U32" t="n">
-        <v>395721.403045</v>
+        <v>395721.513682</v>
       </c>
       <c r="V32" t="n">
-        <v>469121.997461</v>
+        <v>469122.221154</v>
       </c>
     </row>
     <row r="33">
@@ -2882,58 +2882,58 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>16295.72993</v>
+        <v>16295.729941</v>
       </c>
       <c r="F33" t="n">
-        <v>24811.593481</v>
+        <v>24811.593515</v>
       </c>
       <c r="G33" t="n">
-        <v>34628.548858</v>
+        <v>34628.548923</v>
       </c>
       <c r="H33" t="n">
-        <v>47256.097952</v>
+        <v>47256.098064</v>
       </c>
       <c r="I33" t="n">
-        <v>62731.221149</v>
+        <v>62731.221345</v>
       </c>
       <c r="J33" t="n">
-        <v>82266.92481700001</v>
+        <v>82266.925174</v>
       </c>
       <c r="K33" t="n">
-        <v>108950.199773</v>
+        <v>108950.200455</v>
       </c>
       <c r="L33" t="n">
-        <v>142627.884566</v>
+        <v>142627.885901</v>
       </c>
       <c r="M33" t="n">
-        <v>184443.162227</v>
+        <v>184443.164842</v>
       </c>
       <c r="N33" t="n">
-        <v>239683.380748</v>
+        <v>239683.385646</v>
       </c>
       <c r="O33" t="n">
-        <v>311408.041362</v>
+        <v>311408.050168</v>
       </c>
       <c r="P33" t="n">
-        <v>399946.810834</v>
+        <v>399946.826321</v>
       </c>
       <c r="Q33" t="n">
-        <v>506521.224542</v>
+        <v>506521.251829</v>
       </c>
       <c r="R33" t="n">
-        <v>631897.734595</v>
+        <v>631897.783395</v>
       </c>
       <c r="S33" t="n">
-        <v>774691.09342</v>
+        <v>774691.182002</v>
       </c>
       <c r="T33" t="n">
-        <v>932919.511004</v>
+        <v>932919.675167</v>
       </c>
       <c r="U33" t="n">
-        <v>1110340.46956</v>
+        <v>1110340.784391</v>
       </c>
       <c r="V33" t="n">
-        <v>1285516.765372</v>
+        <v>1285517.392996</v>
       </c>
     </row>
     <row r="34">
@@ -2958,58 +2958,58 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>33151.463305</v>
+        <v>33151.463331</v>
       </c>
       <c r="F34" t="n">
-        <v>89028.896043</v>
+        <v>89028.896178</v>
       </c>
       <c r="G34" t="n">
-        <v>210616.56148</v>
+        <v>210616.561923</v>
       </c>
       <c r="H34" t="n">
-        <v>414400.14173</v>
+        <v>414400.142847</v>
       </c>
       <c r="I34" t="n">
-        <v>695911.8008720001</v>
+        <v>695911.803333</v>
       </c>
       <c r="J34" t="n">
-        <v>1054053.577386</v>
+        <v>1054053.582505</v>
       </c>
       <c r="K34" t="n">
-        <v>1522946.843723</v>
+        <v>1522946.854267</v>
       </c>
       <c r="L34" t="n">
-        <v>2098711.100817</v>
+        <v>2098711.122318</v>
       </c>
       <c r="M34" t="n">
-        <v>2802264.925297</v>
+        <v>2802264.968493</v>
       </c>
       <c r="N34" t="n">
-        <v>3722222.161239</v>
+        <v>3722222.243881</v>
       </c>
       <c r="O34" t="n">
-        <v>4922029.302403</v>
+        <v>4922029.454243</v>
       </c>
       <c r="P34" t="n">
-        <v>6416276.002844</v>
+        <v>6416276.275285</v>
       </c>
       <c r="Q34" t="n">
-        <v>8242173.307646</v>
+        <v>8242173.796912</v>
       </c>
       <c r="R34" t="n">
-        <v>10408623.02983</v>
+        <v>10408623.918489</v>
       </c>
       <c r="S34" t="n">
-        <v>12891188.856387</v>
+        <v>12891190.490077</v>
       </c>
       <c r="T34" t="n">
-        <v>15647191.422319</v>
+        <v>15647194.480776</v>
       </c>
       <c r="U34" t="n">
-        <v>18730688.201373</v>
+        <v>18730694.114323</v>
       </c>
       <c r="V34" t="n">
-        <v>21789153.840226</v>
+        <v>21789165.722414</v>
       </c>
     </row>
     <row r="35">
@@ -3034,58 +3034,58 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4072.078169</v>
+        <v>4072.078171</v>
       </c>
       <c r="F35" t="n">
-        <v>7727.14304</v>
+        <v>7727.143048</v>
       </c>
       <c r="G35" t="n">
-        <v>13168.017701</v>
+        <v>13168.017713</v>
       </c>
       <c r="H35" t="n">
-        <v>20244.309996</v>
+        <v>20244.310003</v>
       </c>
       <c r="I35" t="n">
-        <v>28318.715726</v>
+        <v>28318.71572</v>
       </c>
       <c r="J35" t="n">
-        <v>37554.995534</v>
+        <v>37554.995508</v>
       </c>
       <c r="K35" t="n">
-        <v>49461.040324</v>
+        <v>49461.040285</v>
       </c>
       <c r="L35" t="n">
-        <v>64083.312656</v>
+        <v>64083.312635</v>
       </c>
       <c r="M35" t="n">
-        <v>82008.452232</v>
+        <v>82008.452307</v>
       </c>
       <c r="N35" t="n">
-        <v>105660.156564</v>
+        <v>105660.15679</v>
       </c>
       <c r="O35" t="n">
-        <v>136157.219854</v>
+        <v>136157.220237</v>
       </c>
       <c r="P35" t="n">
-        <v>173301.770775</v>
+        <v>173301.771314</v>
       </c>
       <c r="Q35" t="n">
-        <v>217183.479653</v>
+        <v>217183.480459</v>
       </c>
       <c r="R35" t="n">
-        <v>267770.821395</v>
+        <v>267770.822927</v>
       </c>
       <c r="S35" t="n">
-        <v>323884.272833</v>
+        <v>323884.27615</v>
       </c>
       <c r="T35" t="n">
-        <v>384059.425031</v>
+        <v>384059.432502</v>
       </c>
       <c r="U35" t="n">
-        <v>448935.750931</v>
+        <v>448935.767601</v>
       </c>
       <c r="V35" t="n">
-        <v>509777.624301</v>
+        <v>509777.661276</v>
       </c>
     </row>
     <row r="36">
@@ -3113,55 +3113,55 @@
         <v>81.477766</v>
       </c>
       <c r="F36" t="n">
-        <v>125.951495</v>
+        <v>125.951493</v>
       </c>
       <c r="G36" t="n">
-        <v>157.684774</v>
+        <v>157.684771</v>
       </c>
       <c r="H36" t="n">
-        <v>185.51593</v>
+        <v>185.515925</v>
       </c>
       <c r="I36" t="n">
-        <v>212.582701</v>
+        <v>212.582693</v>
       </c>
       <c r="J36" t="n">
-        <v>246.324714</v>
+        <v>246.324701</v>
       </c>
       <c r="K36" t="n">
-        <v>293.366444</v>
+        <v>293.366423</v>
       </c>
       <c r="L36" t="n">
-        <v>349.047679</v>
+        <v>349.047645</v>
       </c>
       <c r="M36" t="n">
-        <v>409.765496</v>
+        <v>409.765441</v>
       </c>
       <c r="N36" t="n">
-        <v>481.125232</v>
+        <v>481.125142</v>
       </c>
       <c r="O36" t="n">
-        <v>565.035283</v>
+        <v>565.035138</v>
       </c>
       <c r="P36" t="n">
-        <v>658.946189</v>
+        <v>658.945952</v>
       </c>
       <c r="Q36" t="n">
-        <v>762.552587</v>
+        <v>762.552199</v>
       </c>
       <c r="R36" t="n">
-        <v>871.969515</v>
+        <v>871.968874</v>
       </c>
       <c r="S36" t="n">
-        <v>980.518136</v>
+        <v>980.517076</v>
       </c>
       <c r="T36" t="n">
-        <v>1083.35486</v>
+        <v>1083.353086</v>
       </c>
       <c r="U36" t="n">
-        <v>1185.09693</v>
+        <v>1185.093852</v>
       </c>
       <c r="V36" t="n">
-        <v>1264.145155</v>
+        <v>1264.139572</v>
       </c>
     </row>
     <row r="37">
@@ -3186,58 +3186,58 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4535.657265</v>
+        <v>4535.657259</v>
       </c>
       <c r="F37" t="n">
-        <v>6110.4462</v>
+        <v>6110.446185</v>
       </c>
       <c r="G37" t="n">
-        <v>7520.392829</v>
+        <v>7520.392802</v>
       </c>
       <c r="H37" t="n">
-        <v>9260.695207000001</v>
+        <v>9260.695159000001</v>
       </c>
       <c r="I37" t="n">
-        <v>11353.394337</v>
+        <v>11353.394253</v>
       </c>
       <c r="J37" t="n">
-        <v>13994.966616</v>
+        <v>13994.966474</v>
       </c>
       <c r="K37" t="n">
-        <v>17614.608481</v>
+        <v>17614.608242</v>
       </c>
       <c r="L37" t="n">
-        <v>22003.220199</v>
+        <v>22003.219814</v>
       </c>
       <c r="M37" t="n">
-        <v>27211.893774</v>
+        <v>27211.893169</v>
       </c>
       <c r="N37" t="n">
-        <v>33950.562848</v>
+        <v>33950.56185</v>
       </c>
       <c r="O37" t="n">
-        <v>42648.461481</v>
+        <v>42648.459737</v>
       </c>
       <c r="P37" t="n">
-        <v>53282.63375</v>
+        <v>53282.630613</v>
       </c>
       <c r="Q37" t="n">
-        <v>65891.229605</v>
+        <v>65891.22394900001</v>
       </c>
       <c r="R37" t="n">
-        <v>80437.008776</v>
+        <v>80436.998697</v>
       </c>
       <c r="S37" t="n">
-        <v>96458.024261</v>
+        <v>96458.006394</v>
       </c>
       <c r="T37" t="n">
-        <v>113635.910935</v>
+        <v>113635.879087</v>
       </c>
       <c r="U37" t="n">
-        <v>132238.140462</v>
+        <v>132238.081603</v>
       </c>
       <c r="V37" t="n">
-        <v>149860.479642</v>
+        <v>149860.365785</v>
       </c>
     </row>
     <row r="38">
@@ -3262,58 +3262,58 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>21688.081156</v>
+        <v>21688.081172</v>
       </c>
       <c r="F38" t="n">
-        <v>34539.046045</v>
+        <v>34539.046095</v>
       </c>
       <c r="G38" t="n">
-        <v>48120.321578</v>
+        <v>48120.321676</v>
       </c>
       <c r="H38" t="n">
-        <v>65712.275799</v>
+        <v>65712.275972</v>
       </c>
       <c r="I38" t="n">
-        <v>88581.344899</v>
+        <v>88581.345212</v>
       </c>
       <c r="J38" t="n">
-        <v>120138.03848</v>
+        <v>120138.039074</v>
       </c>
       <c r="K38" t="n">
-        <v>166354.479612</v>
+        <v>166354.480797</v>
       </c>
       <c r="L38" t="n">
-        <v>228571.507756</v>
+        <v>228571.510172</v>
       </c>
       <c r="M38" t="n">
-        <v>309367.273076</v>
+        <v>309367.277986</v>
       </c>
       <c r="N38" t="n">
-        <v>418931.139593</v>
+        <v>418931.149154</v>
       </c>
       <c r="O38" t="n">
-        <v>565935.460836</v>
+        <v>565935.478766</v>
       </c>
       <c r="P38" t="n">
-        <v>755469.047078</v>
+        <v>755469.079992</v>
       </c>
       <c r="Q38" t="n">
-        <v>996094.958474</v>
+        <v>996095.019024</v>
       </c>
       <c r="R38" t="n">
-        <v>1295347.394833</v>
+        <v>1295347.507705</v>
       </c>
       <c r="S38" t="n">
-        <v>1654614.194245</v>
+        <v>1654614.407266</v>
       </c>
       <c r="T38" t="n">
-        <v>2070568.759205</v>
+        <v>2070569.168245</v>
       </c>
       <c r="U38" t="n">
-        <v>2551214.851278</v>
+        <v>2551215.661068</v>
       </c>
       <c r="V38" t="n">
-        <v>3048064.60598</v>
+        <v>3048066.269442</v>
       </c>
     </row>
     <row r="39">
@@ -3338,58 +3338,58 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1746.004444</v>
+        <v>1746.004445</v>
       </c>
       <c r="F39" t="n">
-        <v>2448.47815</v>
+        <v>2448.478154</v>
       </c>
       <c r="G39" t="n">
-        <v>3211.581769</v>
+        <v>3211.581776</v>
       </c>
       <c r="H39" t="n">
-        <v>4231.23357</v>
+        <v>4231.233582</v>
       </c>
       <c r="I39" t="n">
-        <v>5526.162749</v>
+        <v>5526.162768</v>
       </c>
       <c r="J39" t="n">
-        <v>7215.865076</v>
+        <v>7215.865112</v>
       </c>
       <c r="K39" t="n">
-        <v>9551.69371</v>
+        <v>9551.69378</v>
       </c>
       <c r="L39" t="n">
-        <v>12493.991909</v>
+        <v>12493.992045</v>
       </c>
       <c r="M39" t="n">
-        <v>16091.356471</v>
+        <v>16091.356734</v>
       </c>
       <c r="N39" t="n">
-        <v>20770.60099</v>
+        <v>20770.60148</v>
       </c>
       <c r="O39" t="n">
-        <v>26847.150514</v>
+        <v>26847.151397</v>
       </c>
       <c r="P39" t="n">
-        <v>34453.916979</v>
+        <v>34453.918548</v>
       </c>
       <c r="Q39" t="n">
-        <v>43885.719395</v>
+        <v>43885.7222</v>
       </c>
       <c r="R39" t="n">
-        <v>55345.507012</v>
+        <v>55345.512113</v>
       </c>
       <c r="S39" t="n">
-        <v>68805.55512600001</v>
+        <v>68805.564555</v>
       </c>
       <c r="T39" t="n">
-        <v>84093.67176300001</v>
+        <v>84093.689556</v>
       </c>
       <c r="U39" t="n">
-        <v>101573.822866</v>
+        <v>101573.85762</v>
       </c>
       <c r="V39" t="n">
-        <v>119452.024946</v>
+        <v>119452.095688</v>
       </c>
     </row>
     <row r="40">
@@ -3414,58 +3414,58 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>266.11838</v>
+        <v>266.118381</v>
       </c>
       <c r="F40" t="n">
         <v>409.019491</v>
       </c>
       <c r="G40" t="n">
-        <v>565.552771</v>
+        <v>565.552772</v>
       </c>
       <c r="H40" t="n">
-        <v>751.695649</v>
+        <v>751.695651</v>
       </c>
       <c r="I40" t="n">
-        <v>977.552802</v>
+        <v>977.552806</v>
       </c>
       <c r="J40" t="n">
-        <v>1256.210876</v>
+        <v>1256.210881</v>
       </c>
       <c r="K40" t="n">
-        <v>1644.185448</v>
+        <v>1644.185459</v>
       </c>
       <c r="L40" t="n">
-        <v>2138.983285</v>
+        <v>2138.983306</v>
       </c>
       <c r="M40" t="n">
-        <v>2765.972546</v>
+        <v>2765.972587</v>
       </c>
       <c r="N40" t="n">
-        <v>3601.080301</v>
+        <v>3601.080378</v>
       </c>
       <c r="O40" t="n">
-        <v>4699.368429</v>
+        <v>4699.368569</v>
       </c>
       <c r="P40" t="n">
-        <v>6065.940239</v>
+        <v>6065.940486</v>
       </c>
       <c r="Q40" t="n">
-        <v>7736.548084</v>
+        <v>7736.548521</v>
       </c>
       <c r="R40" t="n">
-        <v>9723.516308</v>
+        <v>9723.517092</v>
       </c>
       <c r="S40" t="n">
-        <v>12002.288964</v>
+        <v>12002.290389</v>
       </c>
       <c r="T40" t="n">
-        <v>14546.936313</v>
+        <v>14546.938955</v>
       </c>
       <c r="U40" t="n">
-        <v>17399.41331</v>
+        <v>17399.418366</v>
       </c>
       <c r="V40" t="n">
-        <v>20261.061797</v>
+        <v>20261.071867</v>
       </c>
     </row>
     <row r="41">
@@ -3496,52 +3496,52 @@
         <v>538.4384</v>
       </c>
       <c r="G41" t="n">
-        <v>776.015447</v>
+        <v>776.015448</v>
       </c>
       <c r="H41" t="n">
-        <v>1060.45259</v>
+        <v>1060.452591</v>
       </c>
       <c r="I41" t="n">
         <v>1395.414173</v>
       </c>
       <c r="J41" t="n">
-        <v>1813.824691</v>
+        <v>1813.82469</v>
       </c>
       <c r="K41" t="n">
-        <v>2382.647352</v>
+        <v>2382.64735</v>
       </c>
       <c r="L41" t="n">
-        <v>3090.814932</v>
+        <v>3090.814931</v>
       </c>
       <c r="M41" t="n">
-        <v>3959.653748</v>
+        <v>3959.653751</v>
       </c>
       <c r="N41" t="n">
-        <v>5095.691047</v>
+        <v>5095.691056</v>
       </c>
       <c r="O41" t="n">
-        <v>6556.60315</v>
+        <v>6556.603165</v>
       </c>
       <c r="P41" t="n">
-        <v>8345.036048</v>
+        <v>8345.036065</v>
       </c>
       <c r="Q41" t="n">
-        <v>10492.786039</v>
+        <v>10492.786058</v>
       </c>
       <c r="R41" t="n">
-        <v>13014.591668</v>
+        <v>13014.591697</v>
       </c>
       <c r="S41" t="n">
-        <v>15878.123468</v>
+        <v>15878.123526</v>
       </c>
       <c r="T41" t="n">
-        <v>19030.099546</v>
+        <v>19030.099685</v>
       </c>
       <c r="U41" t="n">
-        <v>22530.964384</v>
+        <v>22530.964714</v>
       </c>
       <c r="V41" t="n">
-        <v>25934.559204</v>
+        <v>25934.559941</v>
       </c>
     </row>
     <row r="42">
@@ -3566,58 +3566,58 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1731.931669</v>
+        <v>1731.931616</v>
       </c>
       <c r="F42" t="n">
-        <v>2578.915119</v>
+        <v>2578.914956</v>
       </c>
       <c r="G42" t="n">
-        <v>3489.365998</v>
+        <v>3489.365642</v>
       </c>
       <c r="H42" t="n">
-        <v>4599.592325</v>
+        <v>4599.591635</v>
       </c>
       <c r="I42" t="n">
-        <v>5917.831352</v>
+        <v>5917.830087</v>
       </c>
       <c r="J42" t="n">
-        <v>7592.095595</v>
+        <v>7592.093317</v>
       </c>
       <c r="K42" t="n">
-        <v>9835.380979</v>
+        <v>9835.376933</v>
       </c>
       <c r="L42" t="n">
-        <v>12614.420138</v>
+        <v>12614.413122</v>
       </c>
       <c r="M42" t="n">
-        <v>15853.42676</v>
+        <v>15853.414998</v>
       </c>
       <c r="N42" t="n">
-        <v>19920.942104</v>
+        <v>19920.922462</v>
       </c>
       <c r="O42" t="n">
-        <v>25014.792614</v>
+        <v>25014.759629</v>
       </c>
       <c r="P42" t="n">
-        <v>31020.104377</v>
+        <v>31020.04902</v>
       </c>
       <c r="Q42" t="n">
-        <v>37907.389466</v>
+        <v>37907.297316</v>
       </c>
       <c r="R42" t="n">
-        <v>45556.748238</v>
+        <v>45556.59529</v>
       </c>
       <c r="S42" t="n">
-        <v>53701.232444</v>
+        <v>53700.977962</v>
       </c>
       <c r="T42" t="n">
-        <v>62010.97676</v>
+        <v>62010.548163</v>
       </c>
       <c r="U42" t="n">
-        <v>70530.61723800001</v>
+        <v>70529.871618</v>
       </c>
       <c r="V42" t="n">
-        <v>77861.181658</v>
+        <v>77859.82859</v>
       </c>
     </row>
     <row r="43">
@@ -3642,58 +3642,58 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>774.7643849999999</v>
+        <v>774.7643859999999</v>
       </c>
       <c r="F43" t="n">
-        <v>1606.472283</v>
+        <v>1606.472286</v>
       </c>
       <c r="G43" t="n">
-        <v>2875.978486</v>
+        <v>2875.978492</v>
       </c>
       <c r="H43" t="n">
-        <v>4745.36144</v>
+        <v>4745.361453</v>
       </c>
       <c r="I43" t="n">
-        <v>7250.205743</v>
+        <v>7250.205769</v>
       </c>
       <c r="J43" t="n">
-        <v>10611.680105</v>
+        <v>10611.680159</v>
       </c>
       <c r="K43" t="n">
-        <v>15370.568981</v>
+        <v>15370.569094</v>
       </c>
       <c r="L43" t="n">
-        <v>21707.702036</v>
+        <v>21707.702271</v>
       </c>
       <c r="M43" t="n">
-        <v>29944.849376</v>
+        <v>29944.849863</v>
       </c>
       <c r="N43" t="n">
-        <v>41140.412585</v>
+        <v>41140.413548</v>
       </c>
       <c r="O43" t="n">
-        <v>56178.328075</v>
+        <v>56178.329905</v>
       </c>
       <c r="P43" t="n">
-        <v>75488.526627</v>
+        <v>75488.53002000001</v>
       </c>
       <c r="Q43" t="n">
-        <v>99825.51620699999</v>
+        <v>99825.522489</v>
       </c>
       <c r="R43" t="n">
-        <v>129782.531974</v>
+        <v>129782.543722</v>
       </c>
       <c r="S43" t="n">
-        <v>165230.906636</v>
+        <v>165230.928812</v>
       </c>
       <c r="T43" t="n">
-        <v>205441.735793</v>
+        <v>205441.778242</v>
       </c>
       <c r="U43" t="n">
-        <v>250802.642593</v>
+        <v>250802.726135</v>
       </c>
       <c r="V43" t="n">
-        <v>296204.919301</v>
+        <v>296205.089487</v>
       </c>
     </row>
     <row r="44">
@@ -3718,58 +3718,58 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4446.650019</v>
+        <v>4446.650022</v>
       </c>
       <c r="F44" t="n">
-        <v>7369.263881</v>
+        <v>7369.263891</v>
       </c>
       <c r="G44" t="n">
-        <v>10985.84947</v>
+        <v>10985.849492</v>
       </c>
       <c r="H44" t="n">
-        <v>15995.778807</v>
+        <v>15995.778846</v>
       </c>
       <c r="I44" t="n">
-        <v>22553.334063</v>
+        <v>22553.334136</v>
       </c>
       <c r="J44" t="n">
-        <v>31266.628804</v>
+        <v>31266.628946</v>
       </c>
       <c r="K44" t="n">
-        <v>43429.408482</v>
+        <v>43429.408765</v>
       </c>
       <c r="L44" t="n">
-        <v>59112.965088</v>
+        <v>59112.965661</v>
       </c>
       <c r="M44" t="n">
-        <v>78662.479014</v>
+        <v>78662.48016799999</v>
       </c>
       <c r="N44" t="n">
-        <v>104257.575379</v>
+        <v>104257.577587</v>
       </c>
       <c r="O44" t="n">
-        <v>137482.126852</v>
+        <v>137482.130904</v>
       </c>
       <c r="P44" t="n">
-        <v>178738.348217</v>
+        <v>178738.355471</v>
       </c>
       <c r="Q44" t="n">
-        <v>229300.740239</v>
+        <v>229300.75326</v>
       </c>
       <c r="R44" t="n">
-        <v>289894.348931</v>
+        <v>289894.372618</v>
       </c>
       <c r="S44" t="n">
-        <v>360065.239376</v>
+        <v>360065.283053</v>
       </c>
       <c r="T44" t="n">
-        <v>438435.342392</v>
+        <v>438435.424438</v>
       </c>
       <c r="U44" t="n">
-        <v>526246.4768459999</v>
+        <v>526246.635926</v>
       </c>
       <c r="V44" t="n">
-        <v>613260.675813</v>
+        <v>613260.996219</v>
       </c>
     </row>
     <row r="45">
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>534.043039</v>
+        <v>534.04304</v>
       </c>
       <c r="F45" t="n">
         <v>892.365673</v>
@@ -3806,46 +3806,46 @@
         <v>1805.101033</v>
       </c>
       <c r="I45" t="n">
-        <v>2411.729068</v>
+        <v>2411.729066</v>
       </c>
       <c r="J45" t="n">
-        <v>3193.570674</v>
+        <v>3193.570669</v>
       </c>
       <c r="K45" t="n">
-        <v>4304.973843</v>
+        <v>4304.973832</v>
       </c>
       <c r="L45" t="n">
-        <v>5770.83308</v>
+        <v>5770.833058</v>
       </c>
       <c r="M45" t="n">
-        <v>7676.395526</v>
+        <v>7676.395483</v>
       </c>
       <c r="N45" t="n">
-        <v>10149.03205</v>
+        <v>10149.031961</v>
       </c>
       <c r="O45" t="n">
-        <v>13328.700827</v>
+        <v>13328.700638</v>
       </c>
       <c r="P45" t="n">
-        <v>17278.192131</v>
+        <v>17278.191724</v>
       </c>
       <c r="Q45" t="n">
-        <v>22226.189206</v>
+        <v>22226.18834</v>
       </c>
       <c r="R45" t="n">
-        <v>28316.208875</v>
+        <v>28316.207041</v>
       </c>
       <c r="S45" t="n">
-        <v>35569.706215</v>
+        <v>35569.702341</v>
       </c>
       <c r="T45" t="n">
-        <v>43908.941119</v>
+        <v>43908.93292</v>
       </c>
       <c r="U45" t="n">
-        <v>53500.546813</v>
+        <v>53500.528979</v>
       </c>
       <c r="V45" t="n">
-        <v>63332.792582</v>
+        <v>63332.752495</v>
       </c>
     </row>
     <row r="46">
@@ -3876,52 +3876,52 @@
         <v>24.159896</v>
       </c>
       <c r="G46" t="n">
-        <v>36.681534</v>
+        <v>36.681533</v>
       </c>
       <c r="H46" t="n">
         <v>55.712059</v>
       </c>
       <c r="I46" t="n">
-        <v>86.307712</v>
+        <v>86.30771</v>
       </c>
       <c r="J46" t="n">
-        <v>135.38403</v>
+        <v>135.384026</v>
       </c>
       <c r="K46" t="n">
-        <v>214.279923</v>
+        <v>214.279912</v>
       </c>
       <c r="L46" t="n">
-        <v>329.257064</v>
+        <v>329.257034</v>
       </c>
       <c r="M46" t="n">
-        <v>489.186662</v>
+        <v>489.186593</v>
       </c>
       <c r="N46" t="n">
-        <v>715.874766</v>
+        <v>715.874607</v>
       </c>
       <c r="O46" t="n">
-        <v>1029.63102</v>
+        <v>1029.630669</v>
       </c>
       <c r="P46" t="n">
-        <v>1445.649221</v>
+        <v>1445.648468</v>
       </c>
       <c r="Q46" t="n">
-        <v>1983.216689</v>
+        <v>1983.215115</v>
       </c>
       <c r="R46" t="n">
-        <v>2659.414478</v>
+        <v>2659.411242</v>
       </c>
       <c r="S46" t="n">
-        <v>3478.046189</v>
+        <v>3478.039599</v>
       </c>
       <c r="T46" t="n">
-        <v>4429.87397</v>
+        <v>4429.860538</v>
       </c>
       <c r="U46" t="n">
-        <v>5528.272318</v>
+        <v>5528.244405</v>
       </c>
       <c r="V46" t="n">
-        <v>6658.930238</v>
+        <v>6658.870374</v>
       </c>
     </row>
     <row r="47">
@@ -3946,58 +3946,58 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>23879.882997</v>
+        <v>23879.882989</v>
       </c>
       <c r="F47" t="n">
-        <v>43452.386719</v>
+        <v>43452.38664</v>
       </c>
       <c r="G47" t="n">
-        <v>66086.832825</v>
+        <v>66086.832536</v>
       </c>
       <c r="H47" t="n">
-        <v>95643.47431000001</v>
+        <v>95643.47354200001</v>
       </c>
       <c r="I47" t="n">
-        <v>134488.993941</v>
+        <v>134488.992157</v>
       </c>
       <c r="J47" t="n">
-        <v>188642.689135</v>
+        <v>188642.685189</v>
       </c>
       <c r="K47" t="n">
-        <v>269566.522774</v>
+        <v>269566.514048</v>
       </c>
       <c r="L47" t="n">
-        <v>383671.011461</v>
+        <v>383670.992332</v>
       </c>
       <c r="M47" t="n">
-        <v>537285.257976</v>
+        <v>537285.2169079999</v>
       </c>
       <c r="N47" t="n">
-        <v>732489.3247239999</v>
+        <v>732489.242988</v>
       </c>
       <c r="O47" t="n">
-        <v>974550.9433789999</v>
+        <v>974550.789974</v>
       </c>
       <c r="P47" t="n">
-        <v>1266212.760258</v>
+        <v>1266212.481185</v>
       </c>
       <c r="Q47" t="n">
-        <v>1625500.705996</v>
+        <v>1625500.197303</v>
       </c>
       <c r="R47" t="n">
-        <v>2061839.302018</v>
+        <v>2061838.361869</v>
       </c>
       <c r="S47" t="n">
-        <v>2575721.601331</v>
+        <v>2575719.841583</v>
       </c>
       <c r="T47" t="n">
-        <v>3155647.488145</v>
+        <v>3155644.135754</v>
       </c>
       <c r="U47" t="n">
-        <v>3807766.37836</v>
+        <v>3807759.795852</v>
       </c>
       <c r="V47" t="n">
-        <v>4452138.950689</v>
+        <v>4452125.546795</v>
       </c>
     </row>
     <row r="48">
@@ -4025,55 +4025,55 @@
         <v>285.564683</v>
       </c>
       <c r="F48" t="n">
-        <v>447.900777</v>
+        <v>447.900776</v>
       </c>
       <c r="G48" t="n">
-        <v>633.20084</v>
+        <v>633.200838</v>
       </c>
       <c r="H48" t="n">
-        <v>864.2900529999999</v>
+        <v>864.290047</v>
       </c>
       <c r="I48" t="n">
-        <v>1139.547795</v>
+        <v>1139.547785</v>
       </c>
       <c r="J48" t="n">
-        <v>1486.714339</v>
+        <v>1486.71432</v>
       </c>
       <c r="K48" t="n">
-        <v>1968.335069</v>
+        <v>1968.335034</v>
       </c>
       <c r="L48" t="n">
-        <v>2598.931137</v>
+        <v>2598.931074</v>
       </c>
       <c r="M48" t="n">
-        <v>3417.178875</v>
+        <v>3417.178762</v>
       </c>
       <c r="N48" t="n">
-        <v>4540.289515</v>
+        <v>4540.289299</v>
       </c>
       <c r="O48" t="n">
-        <v>6055.097868</v>
+        <v>6055.097443</v>
       </c>
       <c r="P48" t="n">
-        <v>7999.859134</v>
+        <v>7999.858292</v>
       </c>
       <c r="Q48" t="n">
-        <v>10441.839833</v>
+        <v>10441.838178</v>
       </c>
       <c r="R48" t="n">
-        <v>13434.601577</v>
+        <v>13434.598353</v>
       </c>
       <c r="S48" t="n">
-        <v>16987.961869</v>
+        <v>16987.955596</v>
       </c>
       <c r="T48" t="n">
-        <v>21091.574725</v>
+        <v>21091.56238</v>
       </c>
       <c r="U48" t="n">
-        <v>25852.428263</v>
+        <v>25852.403142</v>
       </c>
       <c r="V48" t="n">
-        <v>30821.100356</v>
+        <v>30821.046992</v>
       </c>
     </row>
     <row r="49">
@@ -4098,58 +4098,58 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1050.790096</v>
+        <v>1050.790097</v>
       </c>
       <c r="F49" t="n">
-        <v>1746.549043</v>
+        <v>1746.549045</v>
       </c>
       <c r="G49" t="n">
-        <v>2513.419067</v>
+        <v>2513.419071</v>
       </c>
       <c r="H49" t="n">
-        <v>3431.776843</v>
+        <v>3431.776851</v>
       </c>
       <c r="I49" t="n">
-        <v>4489.761939</v>
+        <v>4489.761952</v>
       </c>
       <c r="J49" t="n">
-        <v>5809.779549</v>
+        <v>5809.779574</v>
       </c>
       <c r="K49" t="n">
-        <v>7629.732511</v>
+        <v>7629.732558</v>
       </c>
       <c r="L49" t="n">
-        <v>9970.135214</v>
+        <v>9970.135307</v>
       </c>
       <c r="M49" t="n">
-        <v>12920.929547</v>
+        <v>12920.929729</v>
       </c>
       <c r="N49" t="n">
-        <v>16883.825881</v>
+        <v>16883.826224</v>
       </c>
       <c r="O49" t="n">
-        <v>22095.259865</v>
+        <v>22095.260488</v>
       </c>
       <c r="P49" t="n">
-        <v>28602.435654</v>
+        <v>28602.436756</v>
       </c>
       <c r="Q49" t="n">
-        <v>36517.729912</v>
+        <v>36517.731865</v>
       </c>
       <c r="R49" t="n">
-        <v>45945.231893</v>
+        <v>45945.235402</v>
       </c>
       <c r="S49" t="n">
-        <v>56786.668162</v>
+        <v>56786.674556</v>
       </c>
       <c r="T49" t="n">
-        <v>68871.829199</v>
+        <v>68871.841072</v>
       </c>
       <c r="U49" t="n">
-        <v>82448.118823</v>
+        <v>82448.141601</v>
       </c>
       <c r="V49" t="n">
-        <v>95959.154674</v>
+        <v>95959.20005</v>
       </c>
     </row>
     <row r="50">
@@ -4204,28 +4204,28 @@
         <v>274.460939</v>
       </c>
       <c r="O50" t="n">
-        <v>352.23803</v>
+        <v>352.238029</v>
       </c>
       <c r="P50" t="n">
-        <v>449.204232</v>
+        <v>449.20423</v>
       </c>
       <c r="Q50" t="n">
-        <v>569.050746</v>
+        <v>569.050739</v>
       </c>
       <c r="R50" t="n">
-        <v>714.674081</v>
+        <v>714.674063</v>
       </c>
       <c r="S50" t="n">
-        <v>886.13929</v>
+        <v>886.139247</v>
       </c>
       <c r="T50" t="n">
-        <v>1081.820441</v>
+        <v>1081.820348</v>
       </c>
       <c r="U50" t="n">
-        <v>1306.848249</v>
+        <v>1306.848038</v>
       </c>
       <c r="V50" t="n">
-        <v>1538.261517</v>
+        <v>1538.26103</v>
       </c>
     </row>
     <row r="51">
@@ -4250,58 +4250,58 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="F51" t="n">
-        <v>8e-06</v>
+        <v>7e-06</v>
       </c>
       <c r="G51" t="n">
-        <v>1.8e-05</v>
+        <v>1.5e-05</v>
       </c>
       <c r="H51" t="n">
-        <v>3.5e-05</v>
+        <v>3.1e-05</v>
       </c>
       <c r="I51" t="n">
-        <v>6.8e-05</v>
+        <v>5.9e-05</v>
       </c>
       <c r="J51" t="n">
-        <v>0.000129</v>
+        <v>0.000113</v>
       </c>
       <c r="K51" t="n">
-        <v>0.00025</v>
+        <v>0.000218</v>
       </c>
       <c r="L51" t="n">
-        <v>0.000475</v>
+        <v>0.000416</v>
       </c>
       <c r="M51" t="n">
-        <v>0.000897</v>
+        <v>0.000784</v>
       </c>
       <c r="N51" t="n">
-        <v>0.001707</v>
+        <v>0.001493</v>
       </c>
       <c r="O51" t="n">
-        <v>0.003259</v>
+        <v>0.00285</v>
       </c>
       <c r="P51" t="n">
-        <v>0.006169</v>
+        <v>0.005396</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.011597</v>
+        <v>0.010143</v>
       </c>
       <c r="R51" t="n">
-        <v>0.021697</v>
+        <v>0.018977</v>
       </c>
       <c r="S51" t="n">
-        <v>0.040649</v>
+        <v>0.035552</v>
       </c>
       <c r="T51" t="n">
-        <v>0.077031</v>
+        <v>0.067372</v>
       </c>
       <c r="U51" t="n">
-        <v>0.150802</v>
+        <v>0.131893</v>
       </c>
       <c r="V51" t="n">
-        <v>0.307781</v>
+        <v>0.269188</v>
       </c>
     </row>
     <row r="52">
@@ -4332,52 +4332,52 @@
         <v>285.525009</v>
       </c>
       <c r="G52" t="n">
-        <v>355.80186</v>
+        <v>355.801861</v>
       </c>
       <c r="H52" t="n">
-        <v>448.754485</v>
+        <v>448.754486</v>
       </c>
       <c r="I52" t="n">
-        <v>568.1954940000001</v>
+        <v>568.195496</v>
       </c>
       <c r="J52" t="n">
-        <v>731.466962</v>
+        <v>731.466965</v>
       </c>
       <c r="K52" t="n">
-        <v>972.095278</v>
+        <v>972.095284</v>
       </c>
       <c r="L52" t="n">
-        <v>1294.950668</v>
+        <v>1294.950681</v>
       </c>
       <c r="M52" t="n">
-        <v>1713.059404</v>
+        <v>1713.05943</v>
       </c>
       <c r="N52" t="n">
-        <v>2277.923381</v>
+        <v>2277.92343</v>
       </c>
       <c r="O52" t="n">
-        <v>3027.240049</v>
+        <v>3027.240138</v>
       </c>
       <c r="P52" t="n">
-        <v>3975.19652</v>
+        <v>3975.196679</v>
       </c>
       <c r="Q52" t="n">
-        <v>5157.21019</v>
+        <v>5157.210473</v>
       </c>
       <c r="R52" t="n">
-        <v>6604.18046</v>
+        <v>6604.180972</v>
       </c>
       <c r="S52" t="n">
-        <v>8324.216050000001</v>
+        <v>8324.216989</v>
       </c>
       <c r="T52" t="n">
-        <v>10308.255434</v>
+        <v>10308.257186</v>
       </c>
       <c r="U52" t="n">
-        <v>12616.211386</v>
+        <v>12616.214765</v>
       </c>
       <c r="V52" t="n">
-        <v>15021.920584</v>
+        <v>15021.927328</v>
       </c>
     </row>
     <row r="53">
@@ -4478,19 +4478,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>112510.845881</v>
+        <v>112510.65809</v>
       </c>
       <c r="F54" t="n">
-        <v>159808.672346</v>
+        <v>159807.968623</v>
       </c>
       <c r="G54" t="n">
-        <v>265204.921993</v>
+        <v>265202.456048</v>
       </c>
       <c r="H54" t="n">
-        <v>431542.503451</v>
+        <v>431534.11929</v>
       </c>
       <c r="I54" t="n">
-        <v>615232.344009</v>
+        <v>615201.420715</v>
       </c>
       <c r="J54" t="n">
         <v>1341884.133815</v>
@@ -4554,19 +4554,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>121043.079719</v>
+        <v>121043.26751</v>
       </c>
       <c r="F55" t="n">
-        <v>159760.194204</v>
+        <v>159760.897927</v>
       </c>
       <c r="G55" t="n">
-        <v>250063.262007</v>
+        <v>250065.727952</v>
       </c>
       <c r="H55" t="n">
-        <v>389011.507749</v>
+        <v>389019.89191</v>
       </c>
       <c r="I55" t="n">
-        <v>535872.938191</v>
+        <v>535903.861485</v>
       </c>
       <c r="J55" t="n">
         <v>90489.668385</v>
@@ -4782,19 +4782,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.004113</v>
+        <v>0.002301</v>
       </c>
       <c r="F58" t="n">
-        <v>0.024226</v>
+        <v>0.013556</v>
       </c>
       <c r="G58" t="n">
-        <v>0.098356</v>
+        <v>0.055038</v>
       </c>
       <c r="H58" t="n">
-        <v>0.357412</v>
+        <v>0.200002</v>
       </c>
       <c r="I58" t="n">
-        <v>1.71187</v>
+        <v>0.957943</v>
       </c>
       <c r="J58" t="n">
         <v>87207.159418</v>
@@ -4858,19 +4858,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.000209</v>
+        <v>0.000117</v>
       </c>
       <c r="F59" t="n">
-        <v>0.001293</v>
+        <v>0.000724</v>
       </c>
       <c r="G59" t="n">
-        <v>0.005483</v>
+        <v>0.003068</v>
       </c>
       <c r="H59" t="n">
-        <v>0.019745</v>
+        <v>0.011049</v>
       </c>
       <c r="I59" t="n">
-        <v>0.092059</v>
+        <v>0.051515</v>
       </c>
       <c r="J59" t="n">
         <v>4574.013449</v>
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.00137</v>
+        <v>0.000766</v>
       </c>
       <c r="F60" t="n">
-        <v>0.005377</v>
+        <v>0.003009</v>
       </c>
       <c r="G60" t="n">
-        <v>0.01447</v>
+        <v>0.008097</v>
       </c>
       <c r="H60" t="n">
-        <v>0.039252</v>
+        <v>0.021965</v>
       </c>
       <c r="I60" t="n">
-        <v>0.157495</v>
+        <v>0.088132</v>
       </c>
       <c r="J60" t="n">
         <v>7311.385475</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>38316.905548</v>
+        <v>38316.913272</v>
       </c>
       <c r="F61" t="n">
-        <v>80848.59286400001</v>
+        <v>80848.636513</v>
       </c>
       <c r="G61" t="n">
-        <v>133263.872108</v>
+        <v>133264.028173</v>
       </c>
       <c r="H61" t="n">
-        <v>185221.418777</v>
+        <v>185221.924266</v>
       </c>
       <c r="I61" t="n">
-        <v>245957.743987</v>
+        <v>245959.921573</v>
       </c>
       <c r="J61" t="n">
         <v>81546.91348800001</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2867.344858</v>
+        <v>2867.336466</v>
       </c>
       <c r="F62" t="n">
-        <v>6463.509674</v>
+        <v>6463.445418</v>
       </c>
       <c r="G62" t="n">
-        <v>11056.233583</v>
+        <v>11055.955954</v>
       </c>
       <c r="H62" t="n">
-        <v>15420.190942</v>
+        <v>15419.222591</v>
       </c>
       <c r="I62" t="n">
-        <v>20031.842462</v>
+        <v>20027.599793</v>
       </c>
       <c r="J62" t="n">
         <v>468947.314999</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4800.363681</v>
+        <v>4800.359608</v>
       </c>
       <c r="F63" t="n">
-        <v>10511.204469</v>
+        <v>10511.177435</v>
       </c>
       <c r="G63" t="n">
-        <v>17356.105852</v>
+        <v>17356.007172</v>
       </c>
       <c r="H63" t="n">
-        <v>24062.080311</v>
+        <v>24061.767732</v>
       </c>
       <c r="I63" t="n">
-        <v>32073.832091</v>
+        <v>32072.479061</v>
       </c>
       <c r="J63" t="n">
         <v>192541.190765</v>
@@ -5238,19 +5238,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.000134</v>
+        <v>7.499999999999999e-05</v>
       </c>
       <c r="F64" t="n">
-        <v>0.000674</v>
+        <v>0.000377</v>
       </c>
       <c r="G64" t="n">
-        <v>0.002334</v>
+        <v>0.001306</v>
       </c>
       <c r="H64" t="n">
-        <v>0.007416</v>
+        <v>0.00415</v>
       </c>
       <c r="I64" t="n">
-        <v>0.032246</v>
+        <v>0.018044</v>
       </c>
       <c r="J64" t="n">
         <v>1542.761379</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>24280.501099</v>
+        <v>24280.505599</v>
       </c>
       <c r="F65" t="n">
-        <v>55599.622134</v>
+        <v>55599.649152</v>
       </c>
       <c r="G65" t="n">
-        <v>101159.679004</v>
+        <v>101159.782526</v>
       </c>
       <c r="H65" t="n">
-        <v>155340.085455</v>
+        <v>155340.446554</v>
       </c>
       <c r="I65" t="n">
-        <v>226866.347061</v>
+        <v>226868.014283</v>
       </c>
       <c r="J65" t="n">
         <v>125954.102617</v>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>14343.780082</v>
+        <v>14343.783736</v>
       </c>
       <c r="F66" t="n">
-        <v>32050.319082</v>
+        <v>32050.340989</v>
       </c>
       <c r="G66" t="n">
-        <v>56952.907656</v>
+        <v>56952.991512</v>
       </c>
       <c r="H66" t="n">
-        <v>85442.294192</v>
+        <v>85442.58382699999</v>
       </c>
       <c r="I66" t="n">
-        <v>122005.476601</v>
+        <v>122006.804556</v>
       </c>
       <c r="J66" t="n">
         <v>15939.578272</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>307.852609</v>
+        <v>307.852653</v>
       </c>
       <c r="F67" t="n">
-        <v>703.5735969999999</v>
+        <v>703.5738270000001</v>
       </c>
       <c r="G67" t="n">
-        <v>1308.742417</v>
+        <v>1308.74313</v>
       </c>
       <c r="H67" t="n">
-        <v>2052.581189</v>
+        <v>2052.583024</v>
       </c>
       <c r="I67" t="n">
-        <v>3044.743067</v>
+        <v>3044.748041</v>
       </c>
       <c r="J67" t="n">
         <v>4164.403026</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1016.631372</v>
+        <v>1016.630712</v>
       </c>
       <c r="F68" t="n">
-        <v>2360.825558</v>
+        <v>2360.81993</v>
       </c>
       <c r="G68" t="n">
-        <v>4524.282411</v>
+        <v>4524.249231</v>
       </c>
       <c r="H68" t="n">
-        <v>7049.134928</v>
+        <v>7048.982134</v>
       </c>
       <c r="I68" t="n">
-        <v>9966.928513000001</v>
+        <v>9966.112646</v>
       </c>
       <c r="J68" t="n">
         <v>109228.109052</v>
@@ -5618,19 +5618,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.000335</v>
+        <v>0.000187</v>
       </c>
       <c r="F69" t="n">
-        <v>0.001964</v>
+        <v>0.001099</v>
       </c>
       <c r="G69" t="n">
-        <v>0.007324</v>
+        <v>0.004098</v>
       </c>
       <c r="H69" t="n">
-        <v>0.023893</v>
+        <v>0.01337</v>
       </c>
       <c r="I69" t="n">
-        <v>0.104418</v>
+        <v>0.058431</v>
       </c>
       <c r="J69" t="n">
         <v>5112.16144</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>8215.366666</v>
+        <v>8215.368875</v>
       </c>
       <c r="F70" t="n">
-        <v>17686.226904</v>
+        <v>17686.239692</v>
       </c>
       <c r="G70" t="n">
-        <v>30352.815946</v>
+        <v>30352.863305</v>
       </c>
       <c r="H70" t="n">
-        <v>43698.052194</v>
+        <v>43698.209272</v>
       </c>
       <c r="I70" t="n">
-        <v>59834.358104</v>
+        <v>59835.049272</v>
       </c>
       <c r="J70" t="n">
         <v>3150.420019</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>24073.356185</v>
+        <v>24073.360429</v>
       </c>
       <c r="F71" t="n">
-        <v>56922.501498</v>
+        <v>56922.525491</v>
       </c>
       <c r="G71" t="n">
-        <v>98489.96960500001</v>
+        <v>98490.054902</v>
       </c>
       <c r="H71" t="n">
-        <v>138628.682765</v>
+        <v>138628.961417</v>
       </c>
       <c r="I71" t="n">
-        <v>183533.156889</v>
+        <v>183534.367245</v>
       </c>
       <c r="J71" t="n">
         <v>103731.082007</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>12647.01276</v>
+        <v>12647.015421</v>
       </c>
       <c r="F72" t="n">
-        <v>25156.549115</v>
+        <v>25156.563339</v>
       </c>
       <c r="G72" t="n">
-        <v>40193.714537</v>
+        <v>40193.76327</v>
       </c>
       <c r="H72" t="n">
-        <v>54747.181074</v>
+        <v>54747.333087</v>
       </c>
       <c r="I72" t="n">
-        <v>72141.147805</v>
+        <v>72141.78305500001</v>
       </c>
       <c r="J72" t="n">
         <v>25926.298783</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>21.49889</v>
+        <v>21.489732</v>
       </c>
       <c r="F73" t="n">
-        <v>35.530113</v>
+        <v>35.498324</v>
       </c>
       <c r="G73" t="n">
-        <v>43.137812</v>
+        <v>43.079525</v>
       </c>
       <c r="H73" t="n">
-        <v>47.202033</v>
+        <v>47.09177</v>
       </c>
       <c r="I73" t="n">
-        <v>55.20297</v>
+        <v>54.843627</v>
       </c>
       <c r="J73" t="n">
         <v>35070.799794</v>
@@ -5998,19 +5998,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>8.899999999999999e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="F74" t="n">
-        <v>0.000757</v>
+        <v>0.000424</v>
       </c>
       <c r="G74" t="n">
-        <v>0.003201</v>
+        <v>0.001791</v>
       </c>
       <c r="H74" t="n">
-        <v>0.010522</v>
+        <v>0.005888</v>
       </c>
       <c r="I74" t="n">
-        <v>0.044463</v>
+        <v>0.024881</v>
       </c>
       <c r="J74" t="n">
         <v>2066.448116</v>
@@ -6074,19 +6074,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>7991.823479</v>
+        <v>7991.830931</v>
       </c>
       <c r="F75" t="n">
-        <v>9234.88924</v>
+        <v>9234.898422</v>
       </c>
       <c r="G75" t="n">
-        <v>12344.515932</v>
+        <v>12344.486275</v>
       </c>
       <c r="H75" t="n">
-        <v>16943.349574</v>
+        <v>16943.172884</v>
       </c>
       <c r="I75" t="n">
-        <v>21026.118367</v>
+        <v>21025.414067</v>
       </c>
       <c r="J75" t="n">
         <v>38360.527868</v>
@@ -6150,19 +6150,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6287.262076</v>
+        <v>6287.07359</v>
       </c>
       <c r="F76" t="n">
-        <v>7487.685315</v>
+        <v>7486.986517</v>
       </c>
       <c r="G76" t="n">
-        <v>8171.41648</v>
+        <v>8169.805861</v>
       </c>
       <c r="H76" t="n">
-        <v>9530.473775</v>
+        <v>9526.732629</v>
       </c>
       <c r="I76" t="n">
-        <v>10924.949352</v>
+        <v>10914.444638</v>
       </c>
       <c r="J76" t="n">
         <v>196022.083511</v>
@@ -6226,19 +6226,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>30570.907043</v>
+        <v>30570.980531</v>
       </c>
       <c r="F77" t="n">
-        <v>40114.697336</v>
+        <v>40114.91157</v>
       </c>
       <c r="G77" t="n">
-        <v>56291.974402</v>
+        <v>56292.408267</v>
       </c>
       <c r="H77" t="n">
-        <v>75142.77965500001</v>
+        <v>75143.683686</v>
       </c>
       <c r="I77" t="n">
-        <v>86535.85848900001</v>
+        <v>86538.17576899999</v>
       </c>
       <c r="J77" t="n">
         <v>56084.058567</v>
@@ -6302,19 +6302,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>34436.758155</v>
+        <v>34436.579861</v>
       </c>
       <c r="F78" t="n">
-        <v>34570.914816</v>
+        <v>34570.382242</v>
       </c>
       <c r="G78" t="n">
-        <v>39207.430378</v>
+        <v>39206.03938</v>
       </c>
       <c r="H78" t="n">
-        <v>48699.656761</v>
+        <v>48695.983843</v>
       </c>
       <c r="I78" t="n">
-        <v>58315.161095</v>
+        <v>58303.921729</v>
       </c>
       <c r="J78" t="n">
         <v>271496.158136</v>
@@ -6378,19 +6378,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>40138.940456</v>
+        <v>40139.061701</v>
       </c>
       <c r="F79" t="n">
-        <v>60684.019282</v>
+        <v>60684.466284</v>
       </c>
       <c r="G79" t="n">
-        <v>106038.545151</v>
+        <v>106039.871505</v>
       </c>
       <c r="H79" t="n">
-        <v>179063.148893</v>
+        <v>179067.10308</v>
       </c>
       <c r="I79" t="n">
-        <v>256365.192219</v>
+        <v>256378.291644</v>
       </c>
       <c r="J79" t="n">
         <v>82972.616675</v>
@@ -6454,19 +6454,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>799.226321</v>
+        <v>799.223334</v>
       </c>
       <c r="F80" t="n">
-        <v>787.574338</v>
+        <v>787.5656770000001</v>
       </c>
       <c r="G80" t="n">
-        <v>910.98639</v>
+        <v>910.962503</v>
       </c>
       <c r="H80" t="n">
-        <v>1185.805608</v>
+        <v>1185.736683</v>
       </c>
       <c r="I80" t="n">
-        <v>1497.412089</v>
+        <v>1497.180528</v>
       </c>
       <c r="J80" t="n">
         <v>6405.889853</v>
@@ -6530,19 +6530,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>61474.001337</v>
+        <v>61474.191408</v>
       </c>
       <c r="F81" t="n">
-        <v>96502.043595</v>
+        <v>96502.77777099999</v>
       </c>
       <c r="G81" t="n">
-        <v>172486.676759</v>
+        <v>172488.946461</v>
       </c>
       <c r="H81" t="n">
-        <v>298809.174397</v>
+        <v>298816.243585</v>
       </c>
       <c r="I81" t="n">
-        <v>441468.701163</v>
+        <v>441493.171284</v>
       </c>
       <c r="J81" t="n">
         <v>107822.022392</v>
@@ -6606,19 +6606,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>11.347484</v>
+        <v>11.305149</v>
       </c>
       <c r="F82" t="n">
-        <v>14.376977</v>
+        <v>14.228397</v>
       </c>
       <c r="G82" t="n">
-        <v>21.634419</v>
+        <v>21.193075</v>
       </c>
       <c r="H82" t="n">
-        <v>38.302318</v>
+        <v>36.980166</v>
       </c>
       <c r="I82" t="n">
-        <v>81.2277</v>
+        <v>76.80536600000001</v>
       </c>
       <c r="J82" t="n">
         <v>84276.62508899999</v>
@@ -6682,19 +6682,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>24680.668649</v>
+        <v>24680.688495</v>
       </c>
       <c r="F83" t="n">
-        <v>38220.494105</v>
+        <v>38220.478124</v>
       </c>
       <c r="G83" t="n">
-        <v>65933.141476</v>
+        <v>65932.60806100001</v>
       </c>
       <c r="H83" t="n">
-        <v>109172.602475</v>
+        <v>109169.656901</v>
       </c>
       <c r="I83" t="n">
-        <v>153246.534292</v>
+        <v>153233.74974</v>
       </c>
       <c r="J83" t="n">
         <v>460321.353821</v>
@@ -6910,19 +6910,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>28444.965763</v>
+        <v>28444.995623</v>
       </c>
       <c r="F86" t="n">
-        <v>37073.716615</v>
+        <v>37073.823574</v>
       </c>
       <c r="G86" t="n">
-        <v>55581.83439</v>
+        <v>55582.183314</v>
       </c>
       <c r="H86" t="n">
-        <v>85692.11053599999</v>
+        <v>85693.26216100001</v>
       </c>
       <c r="I86" t="n">
-        <v>117953.547672</v>
+        <v>117957.731197</v>
       </c>
       <c r="J86" t="n">
         <v>54213.866511</v>
@@ -6986,19 +6986,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1297.158893</v>
+        <v>1297.153865</v>
       </c>
       <c r="F87" t="n">
-        <v>1901.784348</v>
+        <v>1901.762933</v>
       </c>
       <c r="G87" t="n">
-        <v>3277.210608</v>
+        <v>3277.126115</v>
       </c>
       <c r="H87" t="n">
-        <v>5680.936108</v>
+        <v>5680.616312</v>
       </c>
       <c r="I87" t="n">
-        <v>8590.954658000001</v>
+        <v>8589.676609</v>
       </c>
       <c r="J87" t="n">
         <v>40106.342979</v>
@@ -7062,19 +7062,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>30591.280513</v>
+        <v>30591.25411</v>
       </c>
       <c r="F88" t="n">
-        <v>36330.712384</v>
+        <v>36330.648315</v>
       </c>
       <c r="G88" t="n">
-        <v>51361.510886</v>
+        <v>51361.369715</v>
       </c>
       <c r="H88" t="n">
-        <v>78552.378094</v>
+        <v>78552.01816399999</v>
       </c>
       <c r="I88" t="n">
-        <v>110764.823528</v>
+        <v>110763.647805</v>
       </c>
       <c r="J88" t="n">
         <v>164885.436773</v>
@@ -7138,19 +7138,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5064.973065</v>
+        <v>5064.975612</v>
       </c>
       <c r="F89" t="n">
-        <v>6386.335073</v>
+        <v>6386.344559</v>
       </c>
       <c r="G89" t="n">
-        <v>9720.856409</v>
+        <v>9720.888116</v>
       </c>
       <c r="H89" t="n">
-        <v>15304.87396</v>
+        <v>15304.981524</v>
       </c>
       <c r="I89" t="n">
-        <v>21544.055005</v>
+        <v>21544.456248</v>
       </c>
       <c r="J89" t="n">
         <v>17950.503084</v>
@@ -7214,19 +7214,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>10481.638634</v>
+        <v>10481.611899</v>
       </c>
       <c r="F90" t="n">
-        <v>13374.378903</v>
+        <v>13374.287066</v>
       </c>
       <c r="G90" t="n">
-        <v>20776.159835</v>
+        <v>20775.84553</v>
       </c>
       <c r="H90" t="n">
-        <v>33646.676861</v>
+        <v>33645.572868</v>
       </c>
       <c r="I90" t="n">
-        <v>48503.976688</v>
+        <v>48499.731008</v>
       </c>
       <c r="J90" t="n">
         <v>154756.339653</v>
@@ -7290,19 +7290,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5448.115667</v>
+        <v>5448.11168</v>
       </c>
       <c r="F91" t="n">
-        <v>7107.288185</v>
+        <v>7107.273464</v>
       </c>
       <c r="G91" t="n">
-        <v>10784.797512</v>
+        <v>10784.748981</v>
       </c>
       <c r="H91" t="n">
-        <v>16556.444234</v>
+        <v>16556.294406</v>
       </c>
       <c r="I91" t="n">
-        <v>22367.203062</v>
+        <v>22366.716325</v>
       </c>
       <c r="J91" t="n">
         <v>35328.462984</v>
@@ -7366,19 +7366,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>9015.395748000001</v>
+        <v>9015.404049000001</v>
       </c>
       <c r="F92" t="n">
-        <v>11861.812825</v>
+        <v>11861.842575</v>
       </c>
       <c r="G92" t="n">
-        <v>18582.495963</v>
+        <v>18582.594439</v>
       </c>
       <c r="H92" t="n">
-        <v>29326.68577</v>
+        <v>29327.013674</v>
       </c>
       <c r="I92" t="n">
-        <v>40569.371895</v>
+        <v>40570.566537</v>
       </c>
       <c r="J92" t="n">
         <v>23572.398793</v>
@@ -7442,19 +7442,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>331.148032</v>
+        <v>331.145494</v>
       </c>
       <c r="F93" t="n">
-        <v>457.956937</v>
+        <v>457.946987</v>
       </c>
       <c r="G93" t="n">
-        <v>764.010132</v>
+        <v>763.972256</v>
       </c>
       <c r="H93" t="n">
-        <v>1319.653337</v>
+        <v>1319.507023</v>
       </c>
       <c r="I93" t="n">
-        <v>2006.31213</v>
+        <v>2005.704336</v>
       </c>
       <c r="J93" t="n">
         <v>16789.676568</v>
@@ -7518,19 +7518,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>73647.05244499999</v>
+        <v>73646.972872</v>
       </c>
       <c r="F94" t="n">
-        <v>103154.647624</v>
+        <v>103154.304676</v>
       </c>
       <c r="G94" t="n">
-        <v>163791.888208</v>
+        <v>163790.651017</v>
       </c>
       <c r="H94" t="n">
-        <v>262980.168298</v>
+        <v>262975.914039</v>
       </c>
       <c r="I94" t="n">
-        <v>371424.241884</v>
+        <v>371408.628327</v>
       </c>
       <c r="J94" t="n">
         <v>787773.132903</v>
@@ -7594,19 +7594,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>85071.878082</v>
+        <v>85071.97643</v>
       </c>
       <c r="F95" t="n">
-        <v>119374.916939</v>
+        <v>119375.287705</v>
       </c>
       <c r="G95" t="n">
-        <v>192583.336205</v>
+        <v>192584.600621</v>
       </c>
       <c r="H95" t="n">
-        <v>312450.457636</v>
+        <v>312454.749863</v>
       </c>
       <c r="I95" t="n">
-        <v>444477.166241</v>
+        <v>444493.012786</v>
       </c>
       <c r="J95" t="n">
         <v>209233.198373</v>
@@ -7670,19 +7670,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>19610.57967</v>
+        <v>19610.576889</v>
       </c>
       <c r="F96" t="n">
-        <v>24344.397317</v>
+        <v>24344.39437</v>
       </c>
       <c r="G96" t="n">
-        <v>34653.484721</v>
+        <v>34653.499889</v>
       </c>
       <c r="H96" t="n">
-        <v>52561.568616</v>
+        <v>52561.666671</v>
       </c>
       <c r="I96" t="n">
-        <v>73017.941972</v>
+        <v>73018.38430999999</v>
       </c>
       <c r="J96" t="n">
         <v>80562.556131</v>
@@ -7746,19 +7746,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>14139.713489</v>
+        <v>14139.721477</v>
       </c>
       <c r="F97" t="n">
-        <v>16248.085549</v>
+        <v>16248.116476</v>
       </c>
       <c r="G97" t="n">
-        <v>22470.720831</v>
+        <v>22470.825707</v>
       </c>
       <c r="H97" t="n">
-        <v>33928.117251</v>
+        <v>33928.473994</v>
       </c>
       <c r="I97" t="n">
-        <v>47585.745966</v>
+        <v>47587.085212</v>
       </c>
       <c r="J97" t="n">
         <v>30525.245948</v>
@@ -7822,19 +7822,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>157678.812764</v>
+        <v>157679.019591</v>
       </c>
       <c r="F98" t="n">
-        <v>177547.842073</v>
+        <v>177548.49712</v>
       </c>
       <c r="G98" t="n">
-        <v>223436.38354</v>
+        <v>223438.274705</v>
       </c>
       <c r="H98" t="n">
-        <v>276269.071196</v>
+        <v>276274.330944</v>
       </c>
       <c r="I98" t="n">
-        <v>341042.665553</v>
+        <v>341060.485754</v>
       </c>
       <c r="J98" t="n">
         <v>141994.183043</v>
@@ -7898,19 +7898,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>47897.314818</v>
+        <v>47897.200388</v>
       </c>
       <c r="F99" t="n">
-        <v>62419.948698</v>
+        <v>62419.527608</v>
       </c>
       <c r="G99" t="n">
-        <v>91992.769774</v>
+        <v>91991.369233</v>
       </c>
       <c r="H99" t="n">
-        <v>128292.322297</v>
+        <v>128288.040248</v>
       </c>
       <c r="I99" t="n">
-        <v>172077.34353</v>
+        <v>172062.005355</v>
       </c>
       <c r="J99" t="n">
         <v>436753.089719</v>
@@ -7974,19 +7974,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>62754.254735</v>
+        <v>62754.311012</v>
       </c>
       <c r="F100" t="n">
-        <v>70147.435401</v>
+        <v>70147.622147</v>
       </c>
       <c r="G100" t="n">
-        <v>89399.83797199999</v>
+        <v>89400.405178</v>
       </c>
       <c r="H100" t="n">
-        <v>112033.077321</v>
+        <v>112034.718148</v>
       </c>
       <c r="I100" t="n">
-        <v>139829.457215</v>
+        <v>139835.177013</v>
       </c>
       <c r="J100" t="n">
         <v>80513.222452</v>
@@ -8050,19 +8050,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>101161.244842</v>
+        <v>101161.396463</v>
       </c>
       <c r="F101" t="n">
-        <v>121199.472095</v>
+        <v>121199.966994</v>
       </c>
       <c r="G101" t="n">
-        <v>164236.336425</v>
+        <v>164237.823267</v>
       </c>
       <c r="H101" t="n">
-        <v>214688.026403</v>
+        <v>214692.298352</v>
       </c>
       <c r="I101" t="n">
-        <v>274522.450644</v>
+        <v>274537.241741</v>
       </c>
       <c r="J101" t="n">
         <v>111493.388638</v>
@@ -8126,19 +8126,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>305747.522071</v>
+        <v>305747.18604</v>
       </c>
       <c r="F102" t="n">
-        <v>387402.229747</v>
+        <v>387401.066938</v>
       </c>
       <c r="G102" t="n">
-        <v>561120.55879</v>
+        <v>561116.839271</v>
       </c>
       <c r="H102" t="n">
-        <v>779844.300035</v>
+        <v>779833.070226</v>
       </c>
       <c r="I102" t="n">
-        <v>1051857.978701</v>
+        <v>1051817.582755</v>
       </c>
       <c r="J102" t="n">
         <v>1903635.580507</v>
@@ -8202,19 +8202,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>625606.659292</v>
+        <v>625606.862108</v>
       </c>
       <c r="F103" t="n">
-        <v>678893.790176</v>
+        <v>678894.63087</v>
       </c>
       <c r="G103" t="n">
-        <v>830813.276116</v>
+        <v>830816.223896</v>
       </c>
       <c r="H103" t="n">
-        <v>1005833.890728</v>
+        <v>1005843.011852</v>
       </c>
       <c r="I103" t="n">
-        <v>1223151.267563</v>
+        <v>1223183.976215</v>
       </c>
       <c r="J103" t="n">
         <v>925405.335378</v>
@@ -8278,19 +8278,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>49210.709272</v>
+        <v>49210.665444</v>
       </c>
       <c r="F104" t="n">
-        <v>59927.554247</v>
+        <v>59927.411302</v>
       </c>
       <c r="G104" t="n">
-        <v>82789.486302</v>
+        <v>82789.066643</v>
       </c>
       <c r="H104" t="n">
-        <v>111657.300759</v>
+        <v>111656.081006</v>
       </c>
       <c r="I104" t="n">
-        <v>147780.037923</v>
+        <v>147775.69036</v>
       </c>
       <c r="J104" t="n">
         <v>245542.56715</v>
@@ -8354,19 +8354,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>26406.864903</v>
+        <v>26406.841171</v>
       </c>
       <c r="F105" t="n">
-        <v>32680.700868</v>
+        <v>32680.628527</v>
       </c>
       <c r="G105" t="n">
-        <v>46423.976746</v>
+        <v>46423.768547</v>
       </c>
       <c r="H105" t="n">
-        <v>63254.75425</v>
+        <v>63254.189024</v>
       </c>
       <c r="I105" t="n">
-        <v>83805.556885</v>
+        <v>83803.725064</v>
       </c>
       <c r="J105" t="n">
         <v>126801.00771</v>
@@ -8430,19 +8430,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>360892.662447</v>
+        <v>360892.675561</v>
       </c>
       <c r="F106" t="n">
-        <v>460901.998459</v>
+        <v>460901.972639</v>
       </c>
       <c r="G106" t="n">
-        <v>678687.705238</v>
+        <v>678687.349497</v>
       </c>
       <c r="H106" t="n">
-        <v>950359.349394</v>
+        <v>950357.702022</v>
       </c>
       <c r="I106" t="n">
-        <v>1281105.542263</v>
+        <v>1281098.334867</v>
       </c>
       <c r="J106" t="n">
         <v>1692979.01926</v>
@@ -8506,19 +8506,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1427.702984</v>
+        <v>1427.654763</v>
       </c>
       <c r="F107" t="n">
-        <v>1921.000306</v>
+        <v>1920.823078</v>
       </c>
       <c r="G107" t="n">
-        <v>2770.494108</v>
+        <v>2769.950015</v>
       </c>
       <c r="H107" t="n">
-        <v>3806.59104</v>
+        <v>3805.021783</v>
       </c>
       <c r="I107" t="n">
-        <v>5126.472411</v>
+        <v>5120.973564</v>
       </c>
       <c r="J107" t="n">
         <v>87922.00098700001</v>
@@ -8582,19 +8582,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>45360.887697</v>
+        <v>45360.557449</v>
       </c>
       <c r="F108" t="n">
-        <v>55099.77522</v>
+        <v>55098.717029</v>
       </c>
       <c r="G108" t="n">
-        <v>74594.168198</v>
+        <v>74591.168416</v>
       </c>
       <c r="H108" t="n">
-        <v>97382.315238</v>
+        <v>97374.175971</v>
       </c>
       <c r="I108" t="n">
-        <v>124623.220267</v>
+        <v>124596.32783</v>
       </c>
       <c r="J108" t="n">
         <v>524351.458944</v>
@@ -8658,19 +8658,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>80763.259916</v>
+        <v>80763.368271</v>
       </c>
       <c r="F109" t="n">
-        <v>98392.855725</v>
+        <v>98393.212376</v>
       </c>
       <c r="G109" t="n">
-        <v>142302.590608</v>
+        <v>142303.701768</v>
       </c>
       <c r="H109" t="n">
-        <v>203526.472416</v>
+        <v>203529.830648</v>
       </c>
       <c r="I109" t="n">
-        <v>286648.738044</v>
+        <v>286661.003048</v>
       </c>
       <c r="J109" t="n">
         <v>183328.741205</v>
@@ -8734,19 +8734,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>339653.825852</v>
+        <v>339654.450053</v>
       </c>
       <c r="F110" t="n">
-        <v>439526.982464</v>
+        <v>439529.1441</v>
       </c>
       <c r="G110" t="n">
-        <v>648126.9940750001</v>
+        <v>648133.918463</v>
       </c>
       <c r="H110" t="n">
-        <v>905284.069415</v>
+        <v>905304.989314</v>
       </c>
       <c r="I110" t="n">
-        <v>1214117.823328</v>
+        <v>1214192.961189</v>
       </c>
       <c r="J110" t="n">
         <v>372816.784238</v>
@@ -8810,19 +8810,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>321735.674851</v>
+        <v>321735.765557</v>
       </c>
       <c r="F111" t="n">
-        <v>403263.104113</v>
+        <v>403263.401631</v>
       </c>
       <c r="G111" t="n">
-        <v>568032.9768609999</v>
+        <v>568033.934452</v>
       </c>
       <c r="H111" t="n">
-        <v>767092.1759959999</v>
+        <v>767095.181344</v>
       </c>
       <c r="I111" t="n">
-        <v>1013470.690213</v>
+        <v>1013481.919765</v>
       </c>
       <c r="J111" t="n">
         <v>1064984.596592</v>
@@ -8886,19 +8886,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>276267.303556</v>
+        <v>276266.746129</v>
       </c>
       <c r="F112" t="n">
-        <v>351405.199407</v>
+        <v>351403.266641</v>
       </c>
       <c r="G112" t="n">
-        <v>512081.009247</v>
+        <v>512074.770649</v>
       </c>
       <c r="H112" t="n">
-        <v>713244.9075119999</v>
+        <v>713225.983117</v>
       </c>
       <c r="I112" t="n">
-        <v>961465.079457</v>
+        <v>961396.919478</v>
       </c>
       <c r="J112" t="n">
         <v>2202089.948179</v>
@@ -8962,19 +8962,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>980.433115</v>
+        <v>980.331509</v>
       </c>
       <c r="F113" t="n">
-        <v>1595.64021</v>
+        <v>1595.148427</v>
       </c>
       <c r="G113" t="n">
-        <v>2555.174028</v>
+        <v>2553.486108</v>
       </c>
       <c r="H113" t="n">
-        <v>4553.553206</v>
+        <v>4547.403574</v>
       </c>
       <c r="I113" t="n">
-        <v>6607.471184</v>
+        <v>6585.025997</v>
       </c>
       <c r="J113" t="n">
         <v>78332.19985400001</v>
@@ -9038,19 +9038,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1011.964484</v>
+        <v>1011.971481</v>
       </c>
       <c r="F114" t="n">
-        <v>2325.828813</v>
+        <v>2325.871434</v>
       </c>
       <c r="G114" t="n">
-        <v>5553.169729</v>
+        <v>5553.355769</v>
       </c>
       <c r="H114" t="n">
-        <v>12925.924849</v>
+        <v>12926.683637</v>
       </c>
       <c r="I114" t="n">
-        <v>21426.697266</v>
+        <v>21429.502243</v>
       </c>
       <c r="J114" t="n">
         <v>20346.398226</v>
@@ -9114,19 +9114,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>25045.3864</v>
+        <v>25045.48101</v>
       </c>
       <c r="F115" t="n">
-        <v>46840.432356</v>
+        <v>46840.88152</v>
       </c>
       <c r="G115" t="n">
-        <v>93800.757623</v>
+        <v>93802.25950299999</v>
       </c>
       <c r="H115" t="n">
-        <v>197484.514125</v>
+        <v>197489.90497</v>
       </c>
       <c r="I115" t="n">
-        <v>316247.37273</v>
+        <v>316267.01294</v>
       </c>
       <c r="J115" t="n">
         <v>367234.2441</v>
@@ -9190,19 +9190,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>20985.827656</v>
+        <v>20985.828947</v>
       </c>
       <c r="F116" t="n">
-        <v>22480.378661</v>
+        <v>22480.382311</v>
       </c>
       <c r="G116" t="n">
-        <v>29133.659479</v>
+        <v>29133.669448</v>
       </c>
       <c r="H116" t="n">
-        <v>39493.696848</v>
+        <v>39493.72503</v>
       </c>
       <c r="I116" t="n">
-        <v>49176.595079</v>
+        <v>49176.685762</v>
       </c>
       <c r="J116" t="n">
         <v>7738.244738</v>
@@ -9266,19 +9266,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>19761.314075</v>
+        <v>19761.314505</v>
       </c>
       <c r="F117" t="n">
-        <v>26144.643749</v>
+        <v>26144.64483</v>
       </c>
       <c r="G117" t="n">
-        <v>37362.690476</v>
+        <v>37362.693094</v>
       </c>
       <c r="H117" t="n">
-        <v>53241.84006</v>
+        <v>53241.846813</v>
       </c>
       <c r="I117" t="n">
-        <v>67803.430785</v>
+        <v>67803.45114</v>
       </c>
       <c r="J117" t="n">
         <v>68378.50744</v>
@@ -9342,19 +9342,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>26735.449687</v>
+        <v>26735.448899</v>
       </c>
       <c r="F118" t="n">
-        <v>27976.074165</v>
+        <v>27976.072011</v>
       </c>
       <c r="G118" t="n">
-        <v>35201.419145</v>
+        <v>35201.413666</v>
       </c>
       <c r="H118" t="n">
-        <v>46571.522843</v>
+        <v>46571.508357</v>
       </c>
       <c r="I118" t="n">
-        <v>56975.287522</v>
+        <v>56975.243211</v>
       </c>
       <c r="J118" t="n">
         <v>88087.85262799999</v>
@@ -9418,19 +9418,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>7223.169703</v>
+        <v>7223.169713</v>
       </c>
       <c r="F119" t="n">
-        <v>9124.544191999999</v>
+        <v>9124.544083000001</v>
       </c>
       <c r="G119" t="n">
-        <v>13650.743224</v>
+        <v>13650.742503</v>
       </c>
       <c r="H119" t="n">
-        <v>20649.70723</v>
+        <v>20649.704095</v>
       </c>
       <c r="I119" t="n">
-        <v>27796.143471</v>
+        <v>27796.130645</v>
       </c>
       <c r="J119" t="n">
         <v>41942.326223</v>
@@ -9494,19 +9494,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5307.884287</v>
+        <v>5307.884475</v>
       </c>
       <c r="F120" t="n">
-        <v>5723.513904</v>
+        <v>5723.514439</v>
       </c>
       <c r="G120" t="n">
-        <v>7482.524218</v>
+        <v>7482.525696</v>
       </c>
       <c r="H120" t="n">
-        <v>10256.674032</v>
+        <v>10256.678274</v>
       </c>
       <c r="I120" t="n">
-        <v>12938.716323</v>
+        <v>12938.730192</v>
       </c>
       <c r="J120" t="n">
         <v>7542.509827</v>
@@ -9570,19 +9570,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>36005.525194</v>
+        <v>36005.525002</v>
       </c>
       <c r="F121" t="n">
-        <v>44840.31111</v>
+        <v>44840.309691</v>
       </c>
       <c r="G121" t="n">
-        <v>65981.62772999999</v>
+        <v>65981.621319</v>
       </c>
       <c r="H121" t="n">
-        <v>97263.52712899999</v>
+        <v>97263.50354999999</v>
       </c>
       <c r="I121" t="n">
-        <v>126886.712414</v>
+        <v>126886.62641</v>
       </c>
       <c r="J121" t="n">
         <v>199041.8904</v>
@@ -9646,19 +9646,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>297819.760397</v>
+        <v>297819.759459</v>
       </c>
       <c r="F122" t="n">
-        <v>322328.518259</v>
+        <v>322328.516676</v>
       </c>
       <c r="G122" t="n">
-        <v>424161.710878</v>
+        <v>424161.709424</v>
       </c>
       <c r="H122" t="n">
-        <v>587701.376608</v>
+        <v>587701.3786300001</v>
       </c>
       <c r="I122" t="n">
-        <v>752565.232157</v>
+        <v>752565.2503899999</v>
       </c>
       <c r="J122" t="n">
         <v>884764.696494</v>
@@ -9722,19 +9722,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>67020.09458999999</v>
+        <v>67042.051248</v>
       </c>
       <c r="F123" t="n">
-        <v>72904.199175</v>
+        <v>72959.672011</v>
       </c>
       <c r="G123" t="n">
-        <v>83420.816554</v>
+        <v>83537.768899</v>
       </c>
       <c r="H123" t="n">
-        <v>94160.397226</v>
+        <v>94404.24548</v>
       </c>
       <c r="I123" t="n">
-        <v>103413.418421</v>
+        <v>104017.099476</v>
       </c>
       <c r="J123" t="n">
         <v>32557.180245</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>500227.205124</v>
+        <v>500315.155843</v>
       </c>
       <c r="F124" t="n">
-        <v>547217.998246</v>
+        <v>547438.042838</v>
       </c>
       <c r="G124" t="n">
-        <v>621167.715787</v>
+        <v>621617.276446</v>
       </c>
       <c r="H124" t="n">
-        <v>700636.2694540001</v>
+        <v>701551.533752</v>
       </c>
       <c r="I124" t="n">
-        <v>775901.910209</v>
+        <v>778114.745087</v>
       </c>
       <c r="J124" t="n">
         <v>558274.623389</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>148176.480286</v>
+        <v>148066.57291</v>
       </c>
       <c r="F125" t="n">
-        <v>151975.682649</v>
+        <v>151700.165221</v>
       </c>
       <c r="G125" t="n">
-        <v>161221.497529</v>
+        <v>160654.984525</v>
       </c>
       <c r="H125" t="n">
-        <v>177082.56239</v>
+        <v>175923.449838</v>
       </c>
       <c r="I125" t="n">
-        <v>208673.10544</v>
+        <v>205856.589507</v>
       </c>
       <c r="J125" t="n">
         <v>602205.8044359999</v>
@@ -10254,19 +10254,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1090.667618</v>
+        <v>1090.667089</v>
       </c>
       <c r="F130" t="n">
-        <v>10020.81648</v>
+        <v>10020.799692</v>
       </c>
       <c r="G130" t="n">
-        <v>20733.572716</v>
+        <v>20733.471391</v>
       </c>
       <c r="H130" t="n">
-        <v>36466.523758</v>
+        <v>36465.921011</v>
       </c>
       <c r="I130" t="n">
-        <v>56417.273632</v>
+        <v>56411.647011</v>
       </c>
       <c r="J130" t="n">
         <v>3588863.192982</v>
@@ -10330,19 +10330,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1.4e-05</v>
+        <v>3e-06</v>
       </c>
       <c r="F131" t="n">
-        <v>0.00066</v>
+        <v>0.000142</v>
       </c>
       <c r="G131" t="n">
-        <v>0.004222</v>
+        <v>0.000909</v>
       </c>
       <c r="H131" t="n">
-        <v>0.024489</v>
+        <v>0.005272</v>
       </c>
       <c r="I131" t="n">
-        <v>0.218584</v>
+        <v>0.047056</v>
       </c>
       <c r="J131" t="n">
         <v>103559.149867</v>
@@ -10406,19 +10406,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>51229.162036</v>
+        <v>51229.162606</v>
       </c>
       <c r="F132" t="n">
-        <v>432417.647279</v>
+        <v>432417.662747</v>
       </c>
       <c r="G132" t="n">
-        <v>801129.050595</v>
+        <v>801129.130522</v>
       </c>
       <c r="H132" t="n">
-        <v>1259448.62336</v>
+        <v>1259449.048475</v>
       </c>
       <c r="I132" t="n">
-        <v>1766075.82311</v>
+        <v>1766079.512868</v>
       </c>
       <c r="J132" t="n">
         <v>91123.64976</v>
@@ -10482,19 +10482,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>9308.216439</v>
+        <v>9308.216547</v>
       </c>
       <c r="F133" t="n">
-        <v>111952.872531</v>
+        <v>111952.876652</v>
       </c>
       <c r="G133" t="n">
-        <v>288342.663187</v>
+        <v>288342.692144</v>
       </c>
       <c r="H133" t="n">
-        <v>579488.917549</v>
+        <v>579489.1109870001</v>
       </c>
       <c r="I133" t="n">
-        <v>964311.905483</v>
+        <v>964313.882033</v>
       </c>
       <c r="J133" t="n">
         <v>82494.324073</v>
@@ -10558,19 +10558,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4342.409963</v>
+        <v>4342.409976</v>
       </c>
       <c r="F134" t="n">
-        <v>34675.608072</v>
+        <v>34675.608569</v>
       </c>
       <c r="G134" t="n">
-        <v>63569.703603</v>
+        <v>63569.706886</v>
       </c>
       <c r="H134" t="n">
-        <v>102460.93257</v>
+        <v>102460.953321</v>
       </c>
       <c r="I134" t="n">
-        <v>150072.390139</v>
+        <v>150072.595142</v>
       </c>
       <c r="J134" t="n">
         <v>69726.56988900001</v>
@@ -10634,19 +10634,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>643.672286</v>
+        <v>643.672293</v>
       </c>
       <c r="F135" t="n">
-        <v>6976.118164</v>
+        <v>6976.118415</v>
       </c>
       <c r="G135" t="n">
-        <v>16728.869625</v>
+        <v>16728.871264</v>
       </c>
       <c r="H135" t="n">
-        <v>32371.529014</v>
+        <v>32371.539547</v>
       </c>
       <c r="I135" t="n">
-        <v>53393.970244</v>
+        <v>53394.076643</v>
       </c>
       <c r="J135" t="n">
         <v>7052.841491</v>
@@ -10710,19 +10710,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>107.278843</v>
+        <v>107.278743</v>
       </c>
       <c r="F136" t="n">
-        <v>857.775456</v>
+        <v>857.773429</v>
       </c>
       <c r="G136" t="n">
-        <v>1465.447292</v>
+        <v>1465.440856</v>
       </c>
       <c r="H136" t="n">
-        <v>2134.376485</v>
+        <v>2134.356485</v>
       </c>
       <c r="I136" t="n">
-        <v>2868.888442</v>
+        <v>2868.775192</v>
       </c>
       <c r="J136" t="n">
         <v>61557.38496</v>
@@ -10786,19 +10786,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1795.13049</v>
+        <v>1795.130507</v>
       </c>
       <c r="F137" t="n">
-        <v>15719.679059</v>
+        <v>15719.679507</v>
       </c>
       <c r="G137" t="n">
-        <v>29069.129868</v>
+        <v>29069.132196</v>
       </c>
       <c r="H137" t="n">
-        <v>45413.392401</v>
+        <v>45413.405048</v>
       </c>
       <c r="I137" t="n">
-        <v>64167.081446</v>
+        <v>64167.193942</v>
       </c>
       <c r="J137" t="n">
         <v>16119.75218</v>
@@ -10862,19 +10862,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>14.303841</v>
+        <v>14.303831</v>
       </c>
       <c r="F138" t="n">
-        <v>121.762457</v>
+        <v>121.762194</v>
       </c>
       <c r="G138" t="n">
-        <v>226.952763</v>
+        <v>226.951561</v>
       </c>
       <c r="H138" t="n">
-        <v>354.255756</v>
+        <v>354.250682</v>
       </c>
       <c r="I138" t="n">
-        <v>487.549269</v>
+        <v>487.515686</v>
       </c>
       <c r="J138" t="n">
         <v>16328.952534</v>
@@ -10938,19 +10938,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>3.4e-05</v>
+        <v>7e-06</v>
       </c>
       <c r="G139" t="n">
-        <v>0.000205</v>
+        <v>4.4e-05</v>
       </c>
       <c r="H139" t="n">
-        <v>0.001211</v>
+        <v>0.000261</v>
       </c>
       <c r="I139" t="n">
-        <v>0.011262</v>
+        <v>0.002424</v>
       </c>
       <c r="J139" t="n">
         <v>5489.675926</v>
@@ -11014,19 +11014,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>164.494141</v>
+        <v>164.494055</v>
       </c>
       <c r="F140" t="n">
-        <v>1350.105534</v>
+        <v>1350.103662</v>
       </c>
       <c r="G140" t="n">
-        <v>2557.350845</v>
+        <v>2557.342747</v>
       </c>
       <c r="H140" t="n">
-        <v>4301.804289</v>
+        <v>4301.765173</v>
       </c>
       <c r="I140" t="n">
-        <v>6644.56554</v>
+        <v>6644.224829</v>
       </c>
       <c r="J140" t="n">
         <v>230882.243746</v>
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1476.870299</v>
+        <v>1476.870316</v>
       </c>
       <c r="F141" t="n">
-        <v>13632.989089</v>
+        <v>13632.989594</v>
       </c>
       <c r="G141" t="n">
-        <v>28356.910229</v>
+        <v>28356.913143</v>
       </c>
       <c r="H141" t="n">
-        <v>49930.563648</v>
+        <v>49930.580905</v>
       </c>
       <c r="I141" t="n">
-        <v>77415.264049</v>
+        <v>77415.428854</v>
       </c>
       <c r="J141" t="n">
         <v>2675.49621</v>
@@ -11166,19 +11166,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>414.811029</v>
+        <v>414.811033</v>
       </c>
       <c r="F142" t="n">
-        <v>6049.178185</v>
+        <v>6049.17839</v>
       </c>
       <c r="G142" t="n">
-        <v>20303.520849</v>
+        <v>20303.522337</v>
       </c>
       <c r="H142" t="n">
-        <v>49985.798471</v>
+        <v>49985.805833</v>
       </c>
       <c r="I142" t="n">
-        <v>94901.0318</v>
+        <v>94901.07132</v>
       </c>
       <c r="J142" t="n">
         <v>135253.639383</v>
@@ -11470,19 +11470,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>102.408949</v>
+        <v>102.405476</v>
       </c>
       <c r="F146" t="n">
-        <v>107.138928</v>
+        <v>107.129636</v>
       </c>
       <c r="G146" t="n">
-        <v>111.274954</v>
+        <v>111.255432</v>
       </c>
       <c r="H146" t="n">
-        <v>129.203069</v>
+        <v>129.15659</v>
       </c>
       <c r="I146" t="n">
-        <v>162.329284</v>
+        <v>162.178138</v>
       </c>
       <c r="J146" t="n">
         <v>3456.450983</v>
@@ -11546,19 +11546,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1758.784394</v>
+        <v>1758.775005</v>
       </c>
       <c r="F147" t="n">
-        <v>2127.830267</v>
+        <v>2127.799356</v>
       </c>
       <c r="G147" t="n">
-        <v>2494.182213</v>
+        <v>2494.105594</v>
       </c>
       <c r="H147" t="n">
-        <v>3057.719152</v>
+        <v>3057.524742</v>
       </c>
       <c r="I147" t="n">
-        <v>3871.768226</v>
+        <v>3871.136855</v>
       </c>
       <c r="J147" t="n">
         <v>17897.979449</v>
@@ -11622,19 +11622,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>273607.440457</v>
+        <v>273607.453319</v>
       </c>
       <c r="F148" t="n">
-        <v>341981.302955</v>
+        <v>341981.343157</v>
       </c>
       <c r="G148" t="n">
-        <v>425928.644603</v>
+        <v>425928.740745</v>
       </c>
       <c r="H148" t="n">
-        <v>550017.10175</v>
+        <v>550017.342638</v>
       </c>
       <c r="I148" t="n">
-        <v>716839.8444600001</v>
+        <v>716840.626977</v>
       </c>
       <c r="J148" t="n">
         <v>873212.1335380001</v>
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>9144.836069999999</v>
+        <v>9144.765023</v>
       </c>
       <c r="F149" t="n">
-        <v>11073.853954</v>
+        <v>11073.641649</v>
       </c>
       <c r="G149" t="n">
-        <v>14822.543654</v>
+        <v>14821.972465</v>
       </c>
       <c r="H149" t="n">
-        <v>19852.948293</v>
+        <v>19851.369515</v>
       </c>
       <c r="I149" t="n">
-        <v>26360.884092</v>
+        <v>26355.400634</v>
       </c>
       <c r="J149" t="n">
         <v>93157.945691</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>111876.463284</v>
+        <v>111876.153096</v>
       </c>
       <c r="F150" t="n">
-        <v>133750.197708</v>
+        <v>133749.292647</v>
       </c>
       <c r="G150" t="n">
-        <v>175091.219185</v>
+        <v>175088.776199</v>
       </c>
       <c r="H150" t="n">
-        <v>220742.54521</v>
+        <v>220735.981374</v>
       </c>
       <c r="I150" t="n">
-        <v>271921.338032</v>
+        <v>271899.47366</v>
       </c>
       <c r="J150" t="n">
         <v>549306.454134</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>46418.589226</v>
+        <v>46418.488439</v>
       </c>
       <c r="F151" t="n">
-        <v>57736.973291</v>
+        <v>57736.665656</v>
       </c>
       <c r="G151" t="n">
-        <v>78769.488409</v>
+        <v>78768.601003</v>
       </c>
       <c r="H151" t="n">
-        <v>103212.535983</v>
+        <v>103209.981699</v>
       </c>
       <c r="I151" t="n">
-        <v>129372.399775</v>
+        <v>129363.634927</v>
       </c>
       <c r="J151" t="n">
         <v>245269.355919</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>86782.76422500001</v>
+        <v>86782.282335</v>
       </c>
       <c r="F152" t="n">
-        <v>113108.582133</v>
+        <v>113106.936961</v>
       </c>
       <c r="G152" t="n">
-        <v>151558.639791</v>
+        <v>151554.065712</v>
       </c>
       <c r="H152" t="n">
-        <v>190119.590934</v>
+        <v>190107.699033</v>
       </c>
       <c r="I152" t="n">
-        <v>227277.802727</v>
+        <v>227241.117669</v>
       </c>
       <c r="J152" t="n">
         <v>607724.557164</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>189697.993369</v>
+        <v>189698.90379</v>
       </c>
       <c r="F153" t="n">
-        <v>231058.752091</v>
+        <v>231061.647349</v>
       </c>
       <c r="G153" t="n">
-        <v>319258.968876</v>
+        <v>319267.009581</v>
       </c>
       <c r="H153" t="n">
-        <v>438496.370105</v>
+        <v>438518.0234</v>
       </c>
       <c r="I153" t="n">
-        <v>586904.732623</v>
+        <v>586975.241026</v>
       </c>
       <c r="J153" t="n">
         <v>62046.684332</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>43523.913826</v>
+        <v>43523.967316</v>
       </c>
       <c r="F154" t="n">
-        <v>55765.475224</v>
+        <v>55765.650137</v>
       </c>
       <c r="G154" t="n">
-        <v>74752.267664</v>
+        <v>74752.70262</v>
       </c>
       <c r="H154" t="n">
-        <v>94100.757854</v>
+        <v>94101.69336</v>
       </c>
       <c r="I154" t="n">
-        <v>112096.599131</v>
+        <v>112098.888464</v>
       </c>
       <c r="J154" t="n">
         <v>111680.28914</v>
@@ -12154,58 +12154,58 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>50431.005885</v>
+        <v>50431.005985</v>
       </c>
       <c r="F155" t="n">
-        <v>95164.104624</v>
+        <v>95164.105044</v>
       </c>
       <c r="G155" t="n">
-        <v>219586.50752</v>
+        <v>219586.509072</v>
       </c>
       <c r="H155" t="n">
-        <v>373691.131855</v>
+        <v>373691.135652</v>
       </c>
       <c r="I155" t="n">
-        <v>534809.287883</v>
+        <v>534809.295213</v>
       </c>
       <c r="J155" t="n">
-        <v>707606.8593679999</v>
+        <v>707606.872048</v>
       </c>
       <c r="K155" t="n">
-        <v>900299.029559</v>
+        <v>900299.050443</v>
       </c>
       <c r="L155" t="n">
-        <v>1109665.614411</v>
+        <v>1109665.647685</v>
       </c>
       <c r="M155" t="n">
-        <v>1321195.882215</v>
+        <v>1321195.93342</v>
       </c>
       <c r="N155" t="n">
-        <v>1562497.789433</v>
+        <v>1562497.867496</v>
       </c>
       <c r="O155" t="n">
-        <v>1816215.283895</v>
+        <v>1816215.40053</v>
       </c>
       <c r="P155" t="n">
-        <v>2091401.720124</v>
+        <v>2091401.892644</v>
       </c>
       <c r="Q155" t="n">
-        <v>2358751.232963</v>
+        <v>2358751.484123</v>
       </c>
       <c r="R155" t="n">
-        <v>2608511.778823</v>
+        <v>2608512.142354</v>
       </c>
       <c r="S155" t="n">
-        <v>2877262.812362</v>
+        <v>2877263.34832</v>
       </c>
       <c r="T155" t="n">
-        <v>3129413.938996</v>
+        <v>3129414.742327</v>
       </c>
       <c r="U155" t="n">
-        <v>3396428.863873</v>
+        <v>3396430.119256</v>
       </c>
       <c r="V155" t="n">
-        <v>3667722.111788</v>
+        <v>3667724.193648</v>
       </c>
     </row>
     <row r="156">
@@ -12230,58 +12230,58 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>3637.834571</v>
+        <v>3637.834517</v>
       </c>
       <c r="F156" t="n">
-        <v>6400.74696</v>
+        <v>6400.746718</v>
       </c>
       <c r="G156" t="n">
-        <v>13565.756619</v>
+        <v>13565.755699</v>
       </c>
       <c r="H156" t="n">
-        <v>20862.815743</v>
+        <v>20862.813526</v>
       </c>
       <c r="I156" t="n">
-        <v>26891.599398</v>
+        <v>26891.595168</v>
       </c>
       <c r="J156" t="n">
-        <v>32031.06282</v>
+        <v>32031.055484</v>
       </c>
       <c r="K156" t="n">
-        <v>36570.824001</v>
+        <v>36570.811961</v>
       </c>
       <c r="L156" t="n">
-        <v>40383.118628</v>
+        <v>40383.099688</v>
       </c>
       <c r="M156" t="n">
-        <v>43147.316955</v>
+        <v>43147.288274</v>
       </c>
       <c r="N156" t="n">
-        <v>45853.955155</v>
+        <v>45853.912025</v>
       </c>
       <c r="O156" t="n">
-        <v>47894.80678</v>
+        <v>47894.743121</v>
       </c>
       <c r="P156" t="n">
-        <v>49528.209391</v>
+        <v>49528.11612</v>
       </c>
       <c r="Q156" t="n">
-        <v>50134.714635</v>
+        <v>50134.579518</v>
       </c>
       <c r="R156" t="n">
-        <v>49777.630953</v>
+        <v>49777.436335</v>
       </c>
       <c r="S156" t="n">
-        <v>49316.515501</v>
+        <v>49316.230926</v>
       </c>
       <c r="T156" t="n">
-        <v>48257.027962</v>
+        <v>48256.606797</v>
       </c>
       <c r="U156" t="n">
-        <v>47253.267591</v>
+        <v>47252.619351</v>
       </c>
       <c r="V156" t="n">
-        <v>46219.323022</v>
+        <v>46218.266291</v>
       </c>
     </row>
     <row r="157">
@@ -12306,58 +12306,58 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1108.627636</v>
+        <v>1108.627628</v>
       </c>
       <c r="F157" t="n">
-        <v>2459.816274</v>
+        <v>2459.816206</v>
       </c>
       <c r="G157" t="n">
-        <v>6355.635576</v>
+        <v>6355.635155</v>
       </c>
       <c r="H157" t="n">
-        <v>10956.419804</v>
+        <v>10956.418489</v>
       </c>
       <c r="I157" t="n">
-        <v>14784.356267</v>
+        <v>14784.353581</v>
       </c>
       <c r="J157" t="n">
-        <v>17646.885201</v>
+        <v>17646.880781</v>
       </c>
       <c r="K157" t="n">
-        <v>20076.297125</v>
+        <v>20076.290361</v>
       </c>
       <c r="L157" t="n">
-        <v>22291.084438</v>
+        <v>22291.074273</v>
       </c>
       <c r="M157" t="n">
-        <v>24191.922115</v>
+        <v>24191.907</v>
       </c>
       <c r="N157" t="n">
-        <v>26153.890462</v>
+        <v>26153.868026</v>
       </c>
       <c r="O157" t="n">
-        <v>27693.561458</v>
+        <v>27693.528878</v>
       </c>
       <c r="P157" t="n">
-        <v>28868.342802</v>
+        <v>28868.296254</v>
       </c>
       <c r="Q157" t="n">
-        <v>29222.46874</v>
+        <v>29222.403994</v>
       </c>
       <c r="R157" t="n">
-        <v>28814.721163</v>
+        <v>28814.632779</v>
       </c>
       <c r="S157" t="n">
-        <v>28220.055704</v>
+        <v>28219.934192</v>
       </c>
       <c r="T157" t="n">
-        <v>27219.546616</v>
+        <v>27219.378183</v>
       </c>
       <c r="U157" t="n">
-        <v>26184.960991</v>
+        <v>26184.719397</v>
       </c>
       <c r="V157" t="n">
-        <v>25081.840595</v>
+        <v>25081.47478</v>
       </c>
     </row>
     <row r="158">
@@ -12382,58 +12382,58 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>26719.263551</v>
+        <v>26719.263492</v>
       </c>
       <c r="F158" t="n">
-        <v>41640.735096</v>
+        <v>41640.734905</v>
       </c>
       <c r="G158" t="n">
-        <v>77588.334691</v>
+        <v>77588.334198</v>
       </c>
       <c r="H158" t="n">
-        <v>108724.519162</v>
+        <v>108724.51825</v>
       </c>
       <c r="I158" t="n">
-        <v>132362.087319</v>
+        <v>132362.085764</v>
       </c>
       <c r="J158" t="n">
-        <v>152445.452982</v>
+        <v>152445.450296</v>
       </c>
       <c r="K158" t="n">
-        <v>171200.09566</v>
+        <v>171200.091026</v>
       </c>
       <c r="L158" t="n">
-        <v>187475.230833</v>
+        <v>187475.223089</v>
       </c>
       <c r="M158" t="n">
-        <v>198693.38654</v>
+        <v>198693.374317</v>
       </c>
       <c r="N158" t="n">
-        <v>209086.429163</v>
+        <v>209086.410397</v>
       </c>
       <c r="O158" t="n">
-        <v>216322.182969</v>
+        <v>216322.155022</v>
       </c>
       <c r="P158" t="n">
-        <v>221326.4742</v>
+        <v>221326.433462</v>
       </c>
       <c r="Q158" t="n">
-        <v>220907.149483</v>
+        <v>220907.091821</v>
       </c>
       <c r="R158" t="n">
-        <v>216918.00263</v>
+        <v>216917.921294</v>
       </c>
       <c r="S158" t="n">
-        <v>213972.506985</v>
+        <v>213972.388933</v>
       </c>
       <c r="T158" t="n">
-        <v>209789.969983</v>
+        <v>209789.794308</v>
       </c>
       <c r="U158" t="n">
-        <v>206195.879879</v>
+        <v>206195.607615</v>
       </c>
       <c r="V158" t="n">
-        <v>202011.126439</v>
+        <v>202010.683001</v>
       </c>
     </row>
     <row r="159">
@@ -12458,58 +12458,58 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>472.4863</v>
+        <v>472.486298</v>
       </c>
       <c r="F159" t="n">
-        <v>799.693141</v>
+        <v>799.693134</v>
       </c>
       <c r="G159" t="n">
-        <v>1659.425559</v>
+        <v>1659.425533</v>
       </c>
       <c r="H159" t="n">
-        <v>2511.229296</v>
+        <v>2511.229238</v>
       </c>
       <c r="I159" t="n">
-        <v>3217.68746</v>
+        <v>3217.687351</v>
       </c>
       <c r="J159" t="n">
-        <v>3820.024509</v>
+        <v>3820.024323</v>
       </c>
       <c r="K159" t="n">
-        <v>4422.795416</v>
+        <v>4422.795101</v>
       </c>
       <c r="L159" t="n">
-        <v>4980.23211</v>
+        <v>4980.231595</v>
       </c>
       <c r="M159" t="n">
-        <v>5389.372765</v>
+        <v>5389.371973</v>
       </c>
       <c r="N159" t="n">
-        <v>5745.416307</v>
+        <v>5745.415134</v>
       </c>
       <c r="O159" t="n">
-        <v>6011.008534</v>
+        <v>6011.006831</v>
       </c>
       <c r="P159" t="n">
-        <v>6228.732969</v>
+        <v>6228.730505</v>
       </c>
       <c r="Q159" t="n">
-        <v>6281.636082</v>
+        <v>6281.632597</v>
       </c>
       <c r="R159" t="n">
-        <v>6141.485723</v>
+        <v>6141.480952</v>
       </c>
       <c r="S159" t="n">
-        <v>5918.763457</v>
+        <v>5918.757006</v>
       </c>
       <c r="T159" t="n">
-        <v>5579.318425</v>
+        <v>5579.309753</v>
       </c>
       <c r="U159" t="n">
-        <v>5237.43356</v>
+        <v>5237.42153</v>
       </c>
       <c r="V159" t="n">
-        <v>4913.464341</v>
+        <v>4913.446616</v>
       </c>
     </row>
     <row r="160">
@@ -12534,58 +12534,58 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>14438.437058</v>
+        <v>14438.43708</v>
       </c>
       <c r="F160" t="n">
-        <v>26412.713125</v>
+        <v>26412.713213</v>
       </c>
       <c r="G160" t="n">
-        <v>60608.951196</v>
+        <v>60608.951503</v>
       </c>
       <c r="H160" t="n">
-        <v>102631.028301</v>
+        <v>102631.029005</v>
       </c>
       <c r="I160" t="n">
-        <v>145570.675833</v>
+        <v>145570.677082</v>
       </c>
       <c r="J160" t="n">
-        <v>188015.91928</v>
+        <v>188015.921228</v>
       </c>
       <c r="K160" t="n">
-        <v>231369.278399</v>
+        <v>231369.281267</v>
       </c>
       <c r="L160" t="n">
-        <v>273470.13058</v>
+        <v>273470.13467</v>
       </c>
       <c r="M160" t="n">
-        <v>313298.693409</v>
+        <v>313298.699015</v>
       </c>
       <c r="N160" t="n">
-        <v>359527.59648</v>
+        <v>359527.603921</v>
       </c>
       <c r="O160" t="n">
-        <v>409305.916365</v>
+        <v>409305.925618</v>
       </c>
       <c r="P160" t="n">
-        <v>464824.274513</v>
+        <v>464824.285016</v>
       </c>
       <c r="Q160" t="n">
-        <v>519388.992797</v>
+        <v>519389.002647</v>
       </c>
       <c r="R160" t="n">
-        <v>570175.434708</v>
+        <v>570175.440285</v>
       </c>
       <c r="S160" t="n">
-        <v>624816.208541</v>
+        <v>624816.203172</v>
       </c>
       <c r="T160" t="n">
-        <v>676851.542108</v>
+        <v>676851.512721</v>
       </c>
       <c r="U160" t="n">
-        <v>734278.816341</v>
+        <v>734278.7350869999</v>
       </c>
       <c r="V160" t="n">
-        <v>796543.433702</v>
+        <v>796543.23555</v>
       </c>
     </row>
     <row r="161">
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6.834351</v>
+        <v>6.832713</v>
       </c>
       <c r="F162" t="n">
-        <v>5.487563</v>
+        <v>5.485167</v>
       </c>
       <c r="G162" t="n">
-        <v>6.548431</v>
+        <v>6.544127</v>
       </c>
       <c r="H162" t="n">
-        <v>7.982743</v>
+        <v>7.973831</v>
       </c>
       <c r="I162" t="n">
-        <v>10.090005</v>
+        <v>10.062603</v>
       </c>
       <c r="J162" t="n">
         <v>7158.333361</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1008.97513</v>
+        <v>1008.97524</v>
       </c>
       <c r="F163" t="n">
-        <v>1316.690793</v>
+        <v>1316.691099</v>
       </c>
       <c r="G163" t="n">
-        <v>2517.872845</v>
+        <v>2517.873725</v>
       </c>
       <c r="H163" t="n">
-        <v>4146.498573</v>
+        <v>4146.500807</v>
       </c>
       <c r="I163" t="n">
-        <v>6037.984826</v>
+        <v>6037.992128</v>
       </c>
       <c r="J163" t="n">
         <v>5906.528559</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>7129.975507</v>
+        <v>7129.976427</v>
       </c>
       <c r="F164" t="n">
-        <v>10166.497207</v>
+        <v>10166.500201</v>
       </c>
       <c r="G164" t="n">
-        <v>20670.485274</v>
+        <v>20670.49588</v>
       </c>
       <c r="H164" t="n">
-        <v>36472.862932</v>
+        <v>36472.896575</v>
       </c>
       <c r="I164" t="n">
-        <v>57105.39872</v>
+        <v>57105.528677</v>
       </c>
       <c r="J164" t="n">
         <v>42351.702086</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>47893.074259</v>
+        <v>47893.081334</v>
       </c>
       <c r="F165" t="n">
-        <v>60787.593831</v>
+        <v>60787.616042</v>
       </c>
       <c r="G165" t="n">
-        <v>99533.152126</v>
+        <v>99533.224496</v>
       </c>
       <c r="H165" t="n">
-        <v>148976.057209</v>
+        <v>148976.283392</v>
       </c>
       <c r="I165" t="n">
-        <v>210445.531623</v>
+        <v>210446.432891</v>
       </c>
       <c r="J165" t="n">
         <v>7867.216373</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>32776.318231</v>
+        <v>32776.322986</v>
       </c>
       <c r="F166" t="n">
-        <v>38776.585745</v>
+        <v>38776.59961</v>
       </c>
       <c r="G166" t="n">
-        <v>65152.106985</v>
+        <v>65152.152984</v>
       </c>
       <c r="H166" t="n">
-        <v>99107.89432799999</v>
+        <v>99108.03947600001</v>
       </c>
       <c r="I166" t="n">
-        <v>138483.848202</v>
+        <v>138484.418019</v>
       </c>
       <c r="J166" t="n">
         <v>12184.75571</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>50982.258264</v>
+        <v>50982.255867</v>
       </c>
       <c r="F167" t="n">
-        <v>57796.884672</v>
+        <v>57796.875144</v>
       </c>
       <c r="G167" t="n">
-        <v>95280.221386</v>
+        <v>95280.17963</v>
       </c>
       <c r="H167" t="n">
-        <v>147480.429361</v>
+        <v>147480.265723</v>
       </c>
       <c r="I167" t="n">
-        <v>215846.282944</v>
+        <v>215845.525615</v>
       </c>
       <c r="J167" t="n">
         <v>543244.901347</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>307.819886</v>
+        <v>307.81991</v>
       </c>
       <c r="F168" t="n">
-        <v>382.176363</v>
+        <v>382.176423</v>
       </c>
       <c r="G168" t="n">
-        <v>674.312738</v>
+        <v>674.312893</v>
       </c>
       <c r="H168" t="n">
-        <v>1076.509534</v>
+        <v>1076.50991</v>
       </c>
       <c r="I168" t="n">
-        <v>1584.441653</v>
+        <v>1584.442909</v>
       </c>
       <c r="J168" t="n">
         <v>1805.117336</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>71424.56147</v>
+        <v>71424.57038200001</v>
       </c>
       <c r="F169" t="n">
-        <v>86864.088309</v>
+        <v>86864.114399</v>
       </c>
       <c r="G169" t="n">
-        <v>150622.160269</v>
+        <v>150622.247694</v>
       </c>
       <c r="H169" t="n">
-        <v>245669.997719</v>
+        <v>245670.287231</v>
       </c>
       <c r="I169" t="n">
-        <v>380872.714264</v>
+        <v>380873.947828</v>
       </c>
       <c r="J169" t="n">
         <v>155979.692471</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>8663.480511</v>
+        <v>8663.481628</v>
       </c>
       <c r="F170" t="n">
-        <v>13239.316254</v>
+        <v>13239.320137</v>
       </c>
       <c r="G170" t="n">
-        <v>27343.566258</v>
+        <v>27343.580587</v>
       </c>
       <c r="H170" t="n">
-        <v>48123.544178</v>
+        <v>48123.592518</v>
       </c>
       <c r="I170" t="n">
-        <v>75057.15291400001</v>
+        <v>75057.355943</v>
       </c>
       <c r="J170" t="n">
         <v>41653.415637</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>34198.278282</v>
+        <v>34198.281415</v>
       </c>
       <c r="F171" t="n">
-        <v>40357.766392</v>
+        <v>40357.774259</v>
       </c>
       <c r="G171" t="n">
-        <v>67851.208877</v>
+        <v>67851.230501</v>
       </c>
       <c r="H171" t="n">
-        <v>103227.508052</v>
+        <v>103227.565765</v>
       </c>
       <c r="I171" t="n">
-        <v>144597.570624</v>
+        <v>144597.775539</v>
       </c>
       <c r="J171" t="n">
         <v>129572.838733</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3147.759828</v>
+        <v>3147.716398</v>
       </c>
       <c r="F172" t="n">
-        <v>3570.636416</v>
+        <v>3570.496635</v>
       </c>
       <c r="G172" t="n">
-        <v>5621.018507</v>
+        <v>5620.545668</v>
       </c>
       <c r="H172" t="n">
-        <v>8129.001052</v>
+        <v>8127.543372</v>
       </c>
       <c r="I172" t="n">
-        <v>11189.587774</v>
+        <v>11183.967092</v>
       </c>
       <c r="J172" t="n">
         <v>1632411.145067</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>692.62776</v>
+        <v>692.6278579999999</v>
       </c>
       <c r="F173" t="n">
-        <v>1006.201332</v>
+        <v>1006.201675</v>
       </c>
       <c r="G173" t="n">
-        <v>2009.216769</v>
+        <v>2009.218094</v>
       </c>
       <c r="H173" t="n">
-        <v>3472.191244</v>
+        <v>3472.195926</v>
       </c>
       <c r="I173" t="n">
-        <v>5428.432394</v>
+        <v>5428.452807</v>
       </c>
       <c r="J173" t="n">
         <v>1164.36236</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>47821.064497</v>
+        <v>47821.059832</v>
       </c>
       <c r="F174" t="n">
-        <v>53874.510467</v>
+        <v>53874.492441</v>
       </c>
       <c r="G174" t="n">
-        <v>87113.364636</v>
+        <v>87113.290051</v>
       </c>
       <c r="H174" t="n">
-        <v>130928.694967</v>
+        <v>130928.419402</v>
       </c>
       <c r="I174" t="n">
-        <v>185436.633173</v>
+        <v>185435.41491</v>
       </c>
       <c r="J174" t="n">
         <v>655351.244854</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1437.011032</v>
+        <v>1437.011244</v>
       </c>
       <c r="F175" t="n">
-        <v>2458.97139</v>
+        <v>2458.972274</v>
       </c>
       <c r="G175" t="n">
-        <v>5772.720485</v>
+        <v>5772.724528</v>
       </c>
       <c r="H175" t="n">
-        <v>11503.287532</v>
+        <v>11503.303969</v>
       </c>
       <c r="I175" t="n">
-        <v>20342.461762</v>
+        <v>20342.542039</v>
       </c>
       <c r="J175" t="n">
         <v>3831.465404</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>121.894979</v>
+        <v>121.894981</v>
       </c>
       <c r="F176" t="n">
-        <v>129.714513</v>
+        <v>129.714517</v>
       </c>
       <c r="G176" t="n">
         <v>207.707162</v>
       </c>
       <c r="H176" t="n">
-        <v>317.283353</v>
+        <v>317.28331</v>
       </c>
       <c r="I176" t="n">
-        <v>463.013691</v>
+        <v>463.013359</v>
       </c>
       <c r="J176" t="n">
         <v>764.908628</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>191989.72373</v>
+        <v>191989.749478</v>
       </c>
       <c r="F177" t="n">
-        <v>297066.153053</v>
+        <v>297066.244236</v>
       </c>
       <c r="G177" t="n">
-        <v>613441.7879380001</v>
+        <v>613442.12266</v>
       </c>
       <c r="H177" t="n">
-        <v>1049964.452541</v>
+        <v>1049965.534451</v>
       </c>
       <c r="I177" t="n">
-        <v>1554583.549686</v>
+        <v>1554587.824244</v>
       </c>
       <c r="J177" t="n">
         <v>789407.60808</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>306.593785</v>
+        <v>306.593799</v>
       </c>
       <c r="F178" t="n">
-        <v>406.317023</v>
+        <v>406.317044</v>
       </c>
       <c r="G178" t="n">
-        <v>750.8126569999999</v>
+        <v>750.812646</v>
       </c>
       <c r="H178" t="n">
-        <v>1253.213516</v>
+        <v>1253.213258</v>
       </c>
       <c r="I178" t="n">
-        <v>1923.975128</v>
+        <v>1923.973538</v>
       </c>
       <c r="J178" t="n">
         <v>3286.623511</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>211.848498</v>
+        <v>211.848509</v>
       </c>
       <c r="F179" t="n">
-        <v>246.985877</v>
+        <v>246.985897</v>
       </c>
       <c r="G179" t="n">
-        <v>425.105957</v>
+        <v>425.105974</v>
       </c>
       <c r="H179" t="n">
-        <v>670.0974629999999</v>
+        <v>670.097382</v>
       </c>
       <c r="I179" t="n">
-        <v>983.226918</v>
+        <v>983.2261590000001</v>
       </c>
       <c r="J179" t="n">
         <v>1676.436785</v>
@@ -14133,55 +14133,55 @@
         <v>1e-06</v>
       </c>
       <c r="F181" t="n">
-        <v>-2e-06</v>
+        <v>3e-06</v>
       </c>
       <c r="G181" t="n">
-        <v>5e-06</v>
+        <v>3e-06</v>
       </c>
       <c r="H181" t="n">
+        <v>8e-06</v>
+      </c>
+      <c r="I181" t="n">
+        <v>3e-06</v>
+      </c>
+      <c r="J181" t="n">
+        <v>-1e-06</v>
+      </c>
+      <c r="K181" t="n">
         <v>4e-06</v>
       </c>
-      <c r="I181" t="n">
+      <c r="L181" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="M181" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="N181" t="n">
         <v>-1e-06</v>
       </c>
-      <c r="J181" t="n">
-        <v>-2e-06</v>
-      </c>
-      <c r="K181" t="n">
-        <v>2e-06</v>
-      </c>
-      <c r="L181" t="n">
-        <v>2e-06</v>
-      </c>
-      <c r="M181" t="n">
-        <v>5e-06</v>
-      </c>
-      <c r="N181" t="n">
-        <v>-7e-06</v>
-      </c>
       <c r="O181" t="n">
-        <v>1e-06</v>
+        <v>3e-06</v>
       </c>
       <c r="P181" t="n">
-        <v>-0</v>
+        <v>-4e-06</v>
       </c>
       <c r="Q181" t="n">
-        <v>4e-06</v>
+        <v>6e-06</v>
       </c>
       <c r="R181" t="n">
-        <v>-2e-06</v>
+        <v>-4e-06</v>
       </c>
       <c r="S181" t="n">
-        <v>-2e-06</v>
+        <v>-3e-06</v>
       </c>
       <c r="T181" t="n">
-        <v>-4e-06</v>
+        <v>-6e-06</v>
       </c>
       <c r="U181" t="n">
-        <v>3e-06</v>
+        <v>-1e-06</v>
       </c>
       <c r="V181" t="n">
-        <v>5e-06</v>
+        <v>6e-06</v>
       </c>
     </row>
   </sheetData>
